--- a/AAII_Financials/Yearly/ZEPP_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ZEPP_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -715,25 +715,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>572000</v>
+        <v>575900</v>
       </c>
       <c r="E8" s="3">
-        <v>863000</v>
+        <v>868900</v>
       </c>
       <c r="F8" s="3">
-        <v>888300</v>
+        <v>894400</v>
       </c>
       <c r="G8" s="3">
-        <v>802600</v>
+        <v>808000</v>
       </c>
       <c r="H8" s="3">
-        <v>503300</v>
+        <v>506800</v>
       </c>
       <c r="I8" s="3">
-        <v>282900</v>
+        <v>284800</v>
       </c>
       <c r="J8" s="3">
-        <v>214900</v>
+        <v>216400</v>
       </c>
       <c r="K8" s="3">
         <v>128700</v>
@@ -748,25 +748,25 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>461200</v>
+        <v>464300</v>
       </c>
       <c r="E9" s="3">
-        <v>682700</v>
+        <v>687400</v>
       </c>
       <c r="F9" s="3">
-        <v>704300</v>
+        <v>709100</v>
       </c>
       <c r="G9" s="3">
-        <v>599900</v>
+        <v>604000</v>
       </c>
       <c r="H9" s="3">
-        <v>373600</v>
+        <v>376200</v>
       </c>
       <c r="I9" s="3">
-        <v>214600</v>
+        <v>216100</v>
       </c>
       <c r="J9" s="3">
-        <v>176800</v>
+        <v>178000</v>
       </c>
       <c r="K9" s="3">
         <v>112900</v>
@@ -781,25 +781,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>110900</v>
+        <v>111600</v>
       </c>
       <c r="E10" s="3">
-        <v>180300</v>
+        <v>181500</v>
       </c>
       <c r="F10" s="3">
-        <v>184000</v>
+        <v>185300</v>
       </c>
       <c r="G10" s="3">
-        <v>202700</v>
+        <v>204000</v>
       </c>
       <c r="H10" s="3">
-        <v>129700</v>
+        <v>130600</v>
       </c>
       <c r="I10" s="3">
-        <v>68300</v>
+        <v>68800</v>
       </c>
       <c r="J10" s="3">
-        <v>38100</v>
+        <v>38400</v>
       </c>
       <c r="K10" s="3">
         <v>15900</v>
@@ -829,25 +829,25 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>71400</v>
+        <v>71900</v>
       </c>
       <c r="E12" s="3">
-        <v>71100</v>
+        <v>71600</v>
       </c>
       <c r="F12" s="3">
-        <v>74300</v>
+        <v>74800</v>
       </c>
       <c r="G12" s="3">
-        <v>59500</v>
+        <v>59900</v>
       </c>
       <c r="H12" s="3">
-        <v>36300</v>
+        <v>36600</v>
       </c>
       <c r="I12" s="3">
-        <v>21200</v>
+        <v>21400</v>
       </c>
       <c r="J12" s="3">
-        <v>18300</v>
+        <v>18400</v>
       </c>
       <c r="K12" s="3">
         <v>8800</v>
@@ -901,13 +901,13 @@
         <v>0</v>
       </c>
       <c r="F14" s="3">
-        <v>-7800</v>
+        <v>-7900</v>
       </c>
       <c r="G14" s="3">
         <v>400</v>
       </c>
       <c r="H14" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
@@ -973,25 +973,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>630600</v>
+        <v>634900</v>
       </c>
       <c r="E17" s="3">
-        <v>850000</v>
+        <v>855800</v>
       </c>
       <c r="F17" s="3">
-        <v>856500</v>
+        <v>862300</v>
       </c>
       <c r="G17" s="3">
-        <v>719200</v>
+        <v>724100</v>
       </c>
       <c r="H17" s="3">
-        <v>453900</v>
+        <v>457000</v>
       </c>
       <c r="I17" s="3">
-        <v>257800</v>
+        <v>259500</v>
       </c>
       <c r="J17" s="3">
-        <v>213100</v>
+        <v>214500</v>
       </c>
       <c r="K17" s="3">
         <v>134500</v>
@@ -1006,25 +1006,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-58600</v>
+        <v>-59000</v>
       </c>
       <c r="E18" s="3">
-        <v>13000</v>
+        <v>13100</v>
       </c>
       <c r="F18" s="3">
-        <v>31900</v>
+        <v>32100</v>
       </c>
       <c r="G18" s="3">
-        <v>83400</v>
+        <v>84000</v>
       </c>
       <c r="H18" s="3">
-        <v>49500</v>
+        <v>49800</v>
       </c>
       <c r="I18" s="3">
-        <v>25100</v>
+        <v>25300</v>
       </c>
       <c r="J18" s="3">
-        <v>1800</v>
+        <v>1900</v>
       </c>
       <c r="K18" s="3">
         <v>-5800</v>
@@ -1054,25 +1054,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>15000</v>
+        <v>15100</v>
       </c>
       <c r="E20" s="3">
         <v>8000</v>
       </c>
       <c r="F20" s="3">
-        <v>4800</v>
+        <v>4900</v>
       </c>
       <c r="G20" s="3">
         <v>6700</v>
       </c>
       <c r="H20" s="3">
-        <v>3900</v>
+        <v>4000</v>
       </c>
       <c r="I20" s="3">
         <v>1400</v>
       </c>
       <c r="J20" s="3">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="K20" s="3">
         <v>200</v>
@@ -1087,22 +1087,22 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-35500</v>
+        <v>-35700</v>
       </c>
       <c r="E21" s="3">
-        <v>28100</v>
+        <v>28300</v>
       </c>
       <c r="F21" s="3">
-        <v>40400</v>
+        <v>40700</v>
       </c>
       <c r="G21" s="3">
-        <v>92500</v>
+        <v>93100</v>
       </c>
       <c r="H21" s="3">
-        <v>54200</v>
+        <v>54600</v>
       </c>
       <c r="I21" s="3">
-        <v>27000</v>
+        <v>27200</v>
       </c>
       <c r="J21" s="3">
         <v>4300</v>
@@ -1153,22 +1153,22 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-51400</v>
+        <v>-51800</v>
       </c>
       <c r="E23" s="3">
-        <v>14700</v>
+        <v>14800</v>
       </c>
       <c r="F23" s="3">
-        <v>36700</v>
+        <v>36900</v>
       </c>
       <c r="G23" s="3">
-        <v>90100</v>
+        <v>90700</v>
       </c>
       <c r="H23" s="3">
-        <v>53400</v>
+        <v>53700</v>
       </c>
       <c r="I23" s="3">
-        <v>26500</v>
+        <v>26700</v>
       </c>
       <c r="J23" s="3">
         <v>4000</v>
@@ -1186,7 +1186,7 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-9100</v>
+        <v>-9200</v>
       </c>
       <c r="E24" s="3">
         <v>1500</v>
@@ -1201,7 +1201,7 @@
         <v>7200</v>
       </c>
       <c r="I24" s="3">
-        <v>3200</v>
+        <v>3300</v>
       </c>
       <c r="J24" s="3">
         <v>400</v>
@@ -1252,22 +1252,22 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-42300</v>
+        <v>-42600</v>
       </c>
       <c r="E26" s="3">
-        <v>13200</v>
+        <v>13300</v>
       </c>
       <c r="F26" s="3">
-        <v>32400</v>
+        <v>32600</v>
       </c>
       <c r="G26" s="3">
-        <v>79300</v>
+        <v>79900</v>
       </c>
       <c r="H26" s="3">
-        <v>46200</v>
+        <v>46500</v>
       </c>
       <c r="I26" s="3">
-        <v>23300</v>
+        <v>23400</v>
       </c>
       <c r="J26" s="3">
         <v>3600</v>
@@ -1285,22 +1285,22 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-39800</v>
+        <v>-40100</v>
       </c>
       <c r="E27" s="3">
-        <v>19000</v>
+        <v>19200</v>
       </c>
       <c r="F27" s="3">
-        <v>31600</v>
+        <v>31800</v>
       </c>
       <c r="G27" s="3">
-        <v>79100</v>
+        <v>79600</v>
       </c>
       <c r="H27" s="3">
-        <v>15700</v>
+        <v>15800</v>
       </c>
       <c r="I27" s="3">
-        <v>6900</v>
+        <v>7000</v>
       </c>
       <c r="J27" s="3">
         <v>-1700</v>
@@ -1450,25 +1450,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-15000</v>
+        <v>-15100</v>
       </c>
       <c r="E32" s="3">
         <v>-8000</v>
       </c>
       <c r="F32" s="3">
-        <v>-4800</v>
+        <v>-4900</v>
       </c>
       <c r="G32" s="3">
         <v>-6700</v>
       </c>
       <c r="H32" s="3">
-        <v>-3900</v>
+        <v>-4000</v>
       </c>
       <c r="I32" s="3">
         <v>-1400</v>
       </c>
       <c r="J32" s="3">
-        <v>-2100</v>
+        <v>-2200</v>
       </c>
       <c r="K32" s="3">
         <v>-200</v>
@@ -1483,19 +1483,19 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-39800</v>
+        <v>-40100</v>
       </c>
       <c r="E33" s="3">
-        <v>19000</v>
+        <v>19200</v>
       </c>
       <c r="F33" s="3">
-        <v>31600</v>
+        <v>31800</v>
       </c>
       <c r="G33" s="3">
-        <v>79100</v>
+        <v>79600</v>
       </c>
       <c r="H33" s="3">
-        <v>15700</v>
+        <v>15800</v>
       </c>
       <c r="I33" s="3">
         <v>6400</v>
@@ -1549,19 +1549,19 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-39800</v>
+        <v>-40100</v>
       </c>
       <c r="E35" s="3">
-        <v>19000</v>
+        <v>19200</v>
       </c>
       <c r="F35" s="3">
-        <v>31600</v>
+        <v>31800</v>
       </c>
       <c r="G35" s="3">
-        <v>79100</v>
+        <v>79600</v>
       </c>
       <c r="H35" s="3">
-        <v>15700</v>
+        <v>15800</v>
       </c>
       <c r="I35" s="3">
         <v>6400</v>
@@ -1650,25 +1650,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>122400</v>
+        <v>123300</v>
       </c>
       <c r="E41" s="3">
-        <v>203500</v>
+        <v>204800</v>
       </c>
       <c r="F41" s="3">
-        <v>314600</v>
+        <v>316700</v>
       </c>
       <c r="G41" s="3">
-        <v>249000</v>
+        <v>250700</v>
       </c>
       <c r="H41" s="3">
-        <v>212500</v>
+        <v>213900</v>
       </c>
       <c r="I41" s="3">
-        <v>50600</v>
+        <v>50900</v>
       </c>
       <c r="J41" s="3">
-        <v>21100</v>
+        <v>21300</v>
       </c>
       <c r="K41" s="3">
         <v>31600</v>
@@ -1683,13 +1683,13 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>4700</v>
+        <v>4800</v>
       </c>
       <c r="E42" s="3">
         <v>2700</v>
       </c>
       <c r="F42" s="3">
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="G42" s="3">
         <v>2400</v>
@@ -1716,25 +1716,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>120200</v>
+        <v>121000</v>
       </c>
       <c r="E43" s="3">
-        <v>150200</v>
+        <v>151200</v>
       </c>
       <c r="F43" s="3">
-        <v>176700</v>
+        <v>177900</v>
       </c>
       <c r="G43" s="3">
-        <v>229800</v>
+        <v>231300</v>
       </c>
       <c r="H43" s="3">
-        <v>104600</v>
+        <v>105300</v>
       </c>
       <c r="I43" s="3">
-        <v>88500</v>
+        <v>89100</v>
       </c>
       <c r="J43" s="3">
-        <v>68900</v>
+        <v>69300</v>
       </c>
       <c r="K43" s="3">
         <v>29500</v>
@@ -1749,25 +1749,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>141100</v>
+        <v>142100</v>
       </c>
       <c r="E44" s="3">
-        <v>172500</v>
+        <v>173700</v>
       </c>
       <c r="F44" s="3">
-        <v>168100</v>
+        <v>169300</v>
       </c>
       <c r="G44" s="3">
-        <v>123400</v>
+        <v>124300</v>
       </c>
       <c r="H44" s="3">
-        <v>66900</v>
+        <v>67400</v>
       </c>
       <c r="I44" s="3">
-        <v>34500</v>
+        <v>34700</v>
       </c>
       <c r="J44" s="3">
-        <v>26600</v>
+        <v>26700</v>
       </c>
       <c r="K44" s="3">
         <v>12900</v>
@@ -1782,13 +1782,13 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>20100</v>
+        <v>20200</v>
       </c>
       <c r="E45" s="3">
-        <v>13900</v>
+        <v>14000</v>
       </c>
       <c r="F45" s="3">
-        <v>4600</v>
+        <v>4700</v>
       </c>
       <c r="G45" s="3">
         <v>2000</v>
@@ -1815,25 +1815,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>408500</v>
+        <v>411300</v>
       </c>
       <c r="E46" s="3">
-        <v>542800</v>
+        <v>546500</v>
       </c>
       <c r="F46" s="3">
-        <v>666600</v>
+        <v>671200</v>
       </c>
       <c r="G46" s="3">
-        <v>606500</v>
+        <v>610600</v>
       </c>
       <c r="H46" s="3">
-        <v>394600</v>
+        <v>397200</v>
       </c>
       <c r="I46" s="3">
-        <v>178900</v>
+        <v>180100</v>
       </c>
       <c r="J46" s="3">
-        <v>118700</v>
+        <v>119500</v>
       </c>
       <c r="K46" s="3">
         <v>74600</v>
@@ -1848,25 +1848,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>233800</v>
+        <v>235400</v>
       </c>
       <c r="E47" s="3">
-        <v>214400</v>
+        <v>215800</v>
       </c>
       <c r="F47" s="3">
-        <v>61300</v>
+        <v>61700</v>
       </c>
       <c r="G47" s="3">
-        <v>56100</v>
+        <v>56500</v>
       </c>
       <c r="H47" s="3">
-        <v>28900</v>
+        <v>29000</v>
       </c>
       <c r="I47" s="3">
         <v>11800</v>
       </c>
       <c r="J47" s="3">
-        <v>10800</v>
+        <v>10900</v>
       </c>
       <c r="K47" s="3">
         <v>300</v>
@@ -1881,19 +1881,19 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>22900</v>
+        <v>23100</v>
       </c>
       <c r="E48" s="3">
-        <v>33500</v>
+        <v>33700</v>
       </c>
       <c r="F48" s="3">
-        <v>38100</v>
+        <v>38300</v>
       </c>
       <c r="G48" s="3">
-        <v>23900</v>
+        <v>24100</v>
       </c>
       <c r="H48" s="3">
-        <v>5500</v>
+        <v>5600</v>
       </c>
       <c r="I48" s="3">
         <v>4000</v>
@@ -1914,19 +1914,19 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>26100</v>
+        <v>26300</v>
       </c>
       <c r="E49" s="3">
-        <v>27200</v>
+        <v>27300</v>
       </c>
       <c r="F49" s="3">
-        <v>28700</v>
+        <v>28900</v>
       </c>
       <c r="G49" s="3">
         <v>12700</v>
       </c>
       <c r="H49" s="3">
-        <v>9600</v>
+        <v>9700</v>
       </c>
       <c r="I49" s="3">
         <v>1600</v>
@@ -2013,19 +2013,19 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>36000</v>
+        <v>36200</v>
       </c>
       <c r="E52" s="3">
-        <v>22500</v>
+        <v>22700</v>
       </c>
       <c r="F52" s="3">
-        <v>20500</v>
+        <v>20600</v>
       </c>
       <c r="G52" s="3">
-        <v>15400</v>
+        <v>15500</v>
       </c>
       <c r="H52" s="3">
-        <v>11400</v>
+        <v>11500</v>
       </c>
       <c r="I52" s="3">
         <v>6200</v>
@@ -2079,25 +2079,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>727400</v>
+        <v>732300</v>
       </c>
       <c r="E54" s="3">
-        <v>840300</v>
+        <v>846000</v>
       </c>
       <c r="F54" s="3">
-        <v>815200</v>
+        <v>820700</v>
       </c>
       <c r="G54" s="3">
-        <v>714500</v>
+        <v>719400</v>
       </c>
       <c r="H54" s="3">
-        <v>449900</v>
+        <v>453000</v>
       </c>
       <c r="I54" s="3">
-        <v>202400</v>
+        <v>203700</v>
       </c>
       <c r="J54" s="3">
-        <v>134300</v>
+        <v>135300</v>
       </c>
       <c r="K54" s="3">
         <v>76000</v>
@@ -2142,25 +2142,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>68700</v>
+        <v>69200</v>
       </c>
       <c r="E57" s="3">
-        <v>188800</v>
+        <v>190100</v>
       </c>
       <c r="F57" s="3">
-        <v>271000</v>
+        <v>272800</v>
       </c>
       <c r="G57" s="3">
-        <v>278200</v>
+        <v>280100</v>
       </c>
       <c r="H57" s="3">
-        <v>148400</v>
+        <v>149400</v>
       </c>
       <c r="I57" s="3">
-        <v>98900</v>
+        <v>99500</v>
       </c>
       <c r="J57" s="3">
-        <v>75600</v>
+        <v>76100</v>
       </c>
       <c r="K57" s="3">
         <v>37300</v>
@@ -2175,13 +2175,13 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>133700</v>
+        <v>134600</v>
       </c>
       <c r="E58" s="3">
-        <v>63800</v>
+        <v>64200</v>
       </c>
       <c r="F58" s="3">
-        <v>69700</v>
+        <v>70200</v>
       </c>
       <c r="G58" s="3">
         <v>300</v>
@@ -2193,7 +2193,7 @@
         <v>4900</v>
       </c>
       <c r="J58" s="3">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2208,25 +2208,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>28000</v>
+        <v>28200</v>
       </c>
       <c r="E59" s="3">
-        <v>44600</v>
+        <v>44900</v>
       </c>
       <c r="F59" s="3">
-        <v>44500</v>
+        <v>44800</v>
       </c>
       <c r="G59" s="3">
-        <v>64200</v>
+        <v>64600</v>
       </c>
       <c r="H59" s="3">
-        <v>37800</v>
+        <v>38100</v>
       </c>
       <c r="I59" s="3">
-        <v>17400</v>
+        <v>17500</v>
       </c>
       <c r="J59" s="3">
-        <v>10200</v>
+        <v>10300</v>
       </c>
       <c r="K59" s="3">
         <v>2600</v>
@@ -2241,25 +2241,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>230400</v>
+        <v>232000</v>
       </c>
       <c r="E60" s="3">
-        <v>297200</v>
+        <v>299200</v>
       </c>
       <c r="F60" s="3">
-        <v>385200</v>
+        <v>387800</v>
       </c>
       <c r="G60" s="3">
-        <v>342700</v>
+        <v>345000</v>
       </c>
       <c r="H60" s="3">
-        <v>191600</v>
+        <v>192900</v>
       </c>
       <c r="I60" s="3">
-        <v>121100</v>
+        <v>122000</v>
       </c>
       <c r="J60" s="3">
-        <v>87600</v>
+        <v>88200</v>
       </c>
       <c r="K60" s="3">
         <v>39900</v>
@@ -2274,10 +2274,10 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>94500</v>
+        <v>95100</v>
       </c>
       <c r="E61" s="3">
-        <v>100400</v>
+        <v>101000</v>
       </c>
       <c r="F61" s="3">
         <v>8300</v>
@@ -2307,22 +2307,22 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>31700</v>
+        <v>32000</v>
       </c>
       <c r="E62" s="3">
-        <v>37700</v>
+        <v>38000</v>
       </c>
       <c r="F62" s="3">
-        <v>44700</v>
+        <v>45000</v>
       </c>
       <c r="G62" s="3">
-        <v>27000</v>
+        <v>27200</v>
       </c>
       <c r="H62" s="3">
         <v>8500</v>
       </c>
       <c r="I62" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="J62" s="3">
         <v>0</v>
@@ -2439,25 +2439,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>358300</v>
+        <v>360800</v>
       </c>
       <c r="E66" s="3">
-        <v>437000</v>
+        <v>440000</v>
       </c>
       <c r="F66" s="3">
-        <v>438200</v>
+        <v>441200</v>
       </c>
       <c r="G66" s="3">
-        <v>369200</v>
+        <v>371700</v>
       </c>
       <c r="H66" s="3">
-        <v>199900</v>
+        <v>201200</v>
       </c>
       <c r="I66" s="3">
-        <v>122900</v>
+        <v>123700</v>
       </c>
       <c r="J66" s="3">
-        <v>87600</v>
+        <v>88200</v>
       </c>
       <c r="K66" s="3">
         <v>39900</v>
@@ -2568,10 +2568,10 @@
         <v>0</v>
       </c>
       <c r="I70" s="3">
-        <v>48300</v>
+        <v>48600</v>
       </c>
       <c r="J70" s="3">
-        <v>42600</v>
+        <v>42900</v>
       </c>
       <c r="K70" s="3">
         <v>39100</v>
@@ -2619,25 +2619,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>130200</v>
+        <v>131100</v>
       </c>
       <c r="E72" s="3">
-        <v>175500</v>
+        <v>176700</v>
       </c>
       <c r="F72" s="3">
-        <v>156500</v>
+        <v>157600</v>
       </c>
       <c r="G72" s="3">
-        <v>125700</v>
+        <v>126600</v>
       </c>
       <c r="H72" s="3">
-        <v>47000</v>
+        <v>47300</v>
       </c>
       <c r="I72" s="3">
-        <v>18100</v>
+        <v>18200</v>
       </c>
       <c r="J72" s="3">
-        <v>-5000</v>
+        <v>-5100</v>
       </c>
       <c r="K72" s="3">
         <v>-8700</v>
@@ -2751,25 +2751,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>369000</v>
+        <v>371500</v>
       </c>
       <c r="E76" s="3">
-        <v>403200</v>
+        <v>406000</v>
       </c>
       <c r="F76" s="3">
-        <v>377000</v>
+        <v>379600</v>
       </c>
       <c r="G76" s="3">
-        <v>345300</v>
+        <v>347700</v>
       </c>
       <c r="H76" s="3">
-        <v>250100</v>
+        <v>251800</v>
       </c>
       <c r="I76" s="3">
-        <v>31200</v>
+        <v>31400</v>
       </c>
       <c r="J76" s="3">
-        <v>4100</v>
+        <v>4200</v>
       </c>
       <c r="K76" s="3">
         <v>-3000</v>
@@ -2855,19 +2855,19 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-39800</v>
+        <v>-40100</v>
       </c>
       <c r="E81" s="3">
-        <v>19000</v>
+        <v>19200</v>
       </c>
       <c r="F81" s="3">
-        <v>31600</v>
+        <v>31800</v>
       </c>
       <c r="G81" s="3">
-        <v>79100</v>
+        <v>79600</v>
       </c>
       <c r="H81" s="3">
-        <v>15700</v>
+        <v>15800</v>
       </c>
       <c r="I81" s="3">
         <v>6400</v>
@@ -2909,7 +2909,7 @@
         <v>7200</v>
       </c>
       <c r="F83" s="3">
-        <v>3700</v>
+        <v>3800</v>
       </c>
       <c r="G83" s="3">
         <v>2400</v>
@@ -3101,22 +3101,22 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-108800</v>
+        <v>-109500</v>
       </c>
       <c r="E89" s="3">
-        <v>-32100</v>
+        <v>-32300</v>
       </c>
       <c r="F89" s="3">
-        <v>21700</v>
+        <v>21900</v>
       </c>
       <c r="G89" s="3">
-        <v>59100</v>
+        <v>59500</v>
       </c>
       <c r="H89" s="3">
-        <v>97700</v>
+        <v>98400</v>
       </c>
       <c r="I89" s="3">
-        <v>32900</v>
+        <v>33100</v>
       </c>
       <c r="J89" s="3">
         <v>2400</v>
@@ -3155,10 +3155,10 @@
         <v>-6400</v>
       </c>
       <c r="F91" s="3">
-        <v>-11500</v>
+        <v>-11600</v>
       </c>
       <c r="G91" s="3">
-        <v>-4700</v>
+        <v>-4800</v>
       </c>
       <c r="H91" s="3">
         <v>-2400</v>
@@ -3248,25 +3248,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-5800</v>
+        <v>-5900</v>
       </c>
       <c r="E94" s="3">
-        <v>-147600</v>
+        <v>-148700</v>
       </c>
       <c r="F94" s="3">
-        <v>-28600</v>
+        <v>-28800</v>
       </c>
       <c r="G94" s="3">
-        <v>-15600</v>
+        <v>-15700</v>
       </c>
       <c r="H94" s="3">
-        <v>-44900</v>
+        <v>-45200</v>
       </c>
       <c r="I94" s="3">
         <v>-5400</v>
       </c>
       <c r="J94" s="3">
-        <v>-13700</v>
+        <v>-13800</v>
       </c>
       <c r="K94" s="3">
         <v>-700</v>
@@ -3296,7 +3296,7 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-5500</v>
+        <v>-5600</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
@@ -3428,19 +3428,19 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>39900</v>
+        <v>40200</v>
       </c>
       <c r="E100" s="3">
-        <v>76100</v>
+        <v>76600</v>
       </c>
       <c r="F100" s="3">
-        <v>78000</v>
+        <v>78500</v>
       </c>
       <c r="G100" s="3">
-        <v>3500</v>
+        <v>3600</v>
       </c>
       <c r="H100" s="3">
-        <v>88300</v>
+        <v>88900</v>
       </c>
       <c r="I100" s="3">
         <v>2800</v>
@@ -3464,7 +3464,7 @@
         <v>600</v>
       </c>
       <c r="E101" s="3">
-        <v>-2100</v>
+        <v>-2200</v>
       </c>
       <c r="F101" s="3">
         <v>-6000</v>
@@ -3473,7 +3473,7 @@
         <v>1600</v>
       </c>
       <c r="H101" s="3">
-        <v>8300</v>
+        <v>8400</v>
       </c>
       <c r="I101" s="3">
         <v>-400</v>
@@ -3494,25 +3494,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-74000</v>
+        <v>-74500</v>
       </c>
       <c r="E102" s="3">
-        <v>-105800</v>
+        <v>-106500</v>
       </c>
       <c r="F102" s="3">
-        <v>65100</v>
+        <v>65600</v>
       </c>
       <c r="G102" s="3">
-        <v>48600</v>
+        <v>49000</v>
       </c>
       <c r="H102" s="3">
-        <v>149400</v>
+        <v>150500</v>
       </c>
       <c r="I102" s="3">
-        <v>29900</v>
+        <v>30100</v>
       </c>
       <c r="J102" s="3">
-        <v>-9200</v>
+        <v>-9300</v>
       </c>
       <c r="K102" s="3">
         <v>30500</v>

--- a/AAII_Financials/Yearly/ZEPP_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ZEPP_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
   <si>
     <t>ZEPP</t>
   </si>
@@ -656,160 +656,172 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>575900</v>
+        <v>344800</v>
       </c>
       <c r="E8" s="3">
-        <v>868900</v>
+        <v>572400</v>
       </c>
       <c r="F8" s="3">
-        <v>894400</v>
+        <v>863500</v>
       </c>
       <c r="G8" s="3">
-        <v>808000</v>
+        <v>888800</v>
       </c>
       <c r="H8" s="3">
-        <v>506800</v>
+        <v>803000</v>
       </c>
       <c r="I8" s="3">
-        <v>284800</v>
+        <v>503600</v>
       </c>
       <c r="J8" s="3">
+        <v>283100</v>
+      </c>
+      <c r="K8" s="3">
         <v>216400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>128700</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>464300</v>
+        <v>253900</v>
       </c>
       <c r="E9" s="3">
-        <v>687400</v>
+        <v>461400</v>
       </c>
       <c r="F9" s="3">
-        <v>709100</v>
+        <v>683100</v>
       </c>
       <c r="G9" s="3">
-        <v>604000</v>
+        <v>704700</v>
       </c>
       <c r="H9" s="3">
-        <v>376200</v>
+        <v>600200</v>
       </c>
       <c r="I9" s="3">
-        <v>216100</v>
+        <v>373800</v>
       </c>
       <c r="J9" s="3">
+        <v>214700</v>
+      </c>
+      <c r="K9" s="3">
         <v>178000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>112900</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>111600</v>
+        <v>90900</v>
       </c>
       <c r="E10" s="3">
-        <v>181500</v>
+        <v>111000</v>
       </c>
       <c r="F10" s="3">
-        <v>185300</v>
+        <v>180400</v>
       </c>
       <c r="G10" s="3">
-        <v>204000</v>
+        <v>184100</v>
       </c>
       <c r="H10" s="3">
-        <v>130600</v>
+        <v>202800</v>
       </c>
       <c r="I10" s="3">
-        <v>68800</v>
+        <v>129800</v>
       </c>
       <c r="J10" s="3">
+        <v>68300</v>
+      </c>
+      <c r="K10" s="3">
         <v>38400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>15900</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M10" s="3"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -823,41 +835,45 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>71900</v>
+        <v>50000</v>
       </c>
       <c r="E12" s="3">
-        <v>71600</v>
+        <v>71400</v>
       </c>
       <c r="F12" s="3">
-        <v>74800</v>
+        <v>71200</v>
       </c>
       <c r="G12" s="3">
-        <v>59900</v>
+        <v>74300</v>
       </c>
       <c r="H12" s="3">
-        <v>36600</v>
+        <v>59500</v>
       </c>
       <c r="I12" s="3">
-        <v>21400</v>
+        <v>36400</v>
       </c>
       <c r="J12" s="3">
+        <v>21300</v>
+      </c>
+      <c r="K12" s="3">
         <v>18400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>8800</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -888,29 +904,32 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>300</v>
+      </c>
+      <c r="E14" s="3">
         <v>1900</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
-        <v>-7900</v>
+        <v>0</v>
       </c>
       <c r="G14" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="H14" s="3">
         <v>400</v>
       </c>
-      <c r="H14" s="3">
-        <v>1100</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
+      <c r="I14" s="3">
+        <v>1000</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
@@ -921,9 +940,12 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -954,9 +976,12 @@
       <c r="L15" s="3">
         <v>0</v>
       </c>
-      <c r="M15" s="3"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -967,74 +992,81 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>634900</v>
+        <v>373700</v>
       </c>
       <c r="E17" s="3">
-        <v>855800</v>
+        <v>631000</v>
       </c>
       <c r="F17" s="3">
-        <v>862300</v>
+        <v>850500</v>
       </c>
       <c r="G17" s="3">
-        <v>724100</v>
+        <v>857000</v>
       </c>
       <c r="H17" s="3">
-        <v>457000</v>
+        <v>719600</v>
       </c>
       <c r="I17" s="3">
-        <v>259500</v>
+        <v>454200</v>
       </c>
       <c r="J17" s="3">
+        <v>257900</v>
+      </c>
+      <c r="K17" s="3">
         <v>214500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>134500</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M17" s="3"/>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-59000</v>
+        <v>-28900</v>
       </c>
       <c r="E18" s="3">
-        <v>13100</v>
+        <v>-58600</v>
       </c>
       <c r="F18" s="3">
-        <v>32100</v>
+        <v>13000</v>
       </c>
       <c r="G18" s="3">
-        <v>84000</v>
+        <v>31900</v>
       </c>
       <c r="H18" s="3">
-        <v>49800</v>
+        <v>83400</v>
       </c>
       <c r="I18" s="3">
-        <v>25300</v>
+        <v>49500</v>
       </c>
       <c r="J18" s="3">
+        <v>25100</v>
+      </c>
+      <c r="K18" s="3">
         <v>1900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-5800</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M18" s="3"/>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3"/>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1048,86 +1080,93 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>15100</v>
+        <v>2800</v>
       </c>
       <c r="E20" s="3">
+        <v>15000</v>
+      </c>
+      <c r="F20" s="3">
         <v>8000</v>
       </c>
-      <c r="F20" s="3">
-        <v>4900</v>
-      </c>
       <c r="G20" s="3">
+        <v>4800</v>
+      </c>
+      <c r="H20" s="3">
         <v>6700</v>
       </c>
-      <c r="H20" s="3">
-        <v>4000</v>
-      </c>
       <c r="I20" s="3">
+        <v>3900</v>
+      </c>
+      <c r="J20" s="3">
         <v>1400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M20" s="3"/>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-35700</v>
+        <v>-18600</v>
       </c>
       <c r="E21" s="3">
-        <v>28300</v>
+        <v>-35500</v>
       </c>
       <c r="F21" s="3">
-        <v>40700</v>
+        <v>28100</v>
       </c>
       <c r="G21" s="3">
-        <v>93100</v>
+        <v>40400</v>
       </c>
       <c r="H21" s="3">
-        <v>54600</v>
+        <v>92500</v>
       </c>
       <c r="I21" s="3">
-        <v>27200</v>
+        <v>54300</v>
       </c>
       <c r="J21" s="3">
+        <v>27000</v>
+      </c>
+      <c r="K21" s="3">
         <v>4300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-5500</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M21" s="3"/>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E22" s="3">
         <v>7900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>6200</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1143,78 +1182,87 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3"/>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3"/>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-51800</v>
+        <v>-32700</v>
       </c>
       <c r="E23" s="3">
-        <v>14800</v>
+        <v>-51500</v>
       </c>
       <c r="F23" s="3">
-        <v>36900</v>
+        <v>14700</v>
       </c>
       <c r="G23" s="3">
-        <v>90700</v>
+        <v>36700</v>
       </c>
       <c r="H23" s="3">
-        <v>53700</v>
+        <v>90100</v>
       </c>
       <c r="I23" s="3">
-        <v>26700</v>
+        <v>53400</v>
       </c>
       <c r="J23" s="3">
+        <v>26500</v>
+      </c>
+      <c r="K23" s="3">
         <v>4000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5600</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M23" s="3"/>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-9200</v>
+        <v>-2200</v>
       </c>
       <c r="E24" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="F24" s="3">
         <v>1500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>10800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>7200</v>
       </c>
-      <c r="I24" s="3">
-        <v>3300</v>
-      </c>
       <c r="J24" s="3">
+        <v>3200</v>
+      </c>
+      <c r="K24" s="3">
         <v>400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-100</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M24" s="3"/>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1245,75 +1293,84 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-      <c r="M25" s="3"/>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-42600</v>
+        <v>-30500</v>
       </c>
       <c r="E26" s="3">
+        <v>-42400</v>
+      </c>
+      <c r="F26" s="3">
         <v>13300</v>
       </c>
-      <c r="F26" s="3">
-        <v>32600</v>
-      </c>
       <c r="G26" s="3">
-        <v>79900</v>
+        <v>32400</v>
       </c>
       <c r="H26" s="3">
-        <v>46500</v>
+        <v>79400</v>
       </c>
       <c r="I26" s="3">
-        <v>23400</v>
+        <v>46200</v>
       </c>
       <c r="J26" s="3">
+        <v>23300</v>
+      </c>
+      <c r="K26" s="3">
         <v>3600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5400</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M26" s="3"/>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-40100</v>
+        <v>-29300</v>
       </c>
       <c r="E27" s="3">
-        <v>19200</v>
+        <v>-39800</v>
       </c>
       <c r="F27" s="3">
-        <v>31800</v>
+        <v>19000</v>
       </c>
       <c r="G27" s="3">
-        <v>79600</v>
+        <v>31600</v>
       </c>
       <c r="H27" s="3">
-        <v>15800</v>
+        <v>79100</v>
       </c>
       <c r="I27" s="3">
+        <v>15700</v>
+      </c>
+      <c r="J27" s="3">
         <v>7000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-8800</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M27" s="3"/>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N27" s="3"/>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1344,9 +1401,12 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-      <c r="M28" s="3"/>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3"/>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1365,21 +1425,24 @@
       <c r="H29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I29" s="3">
+      <c r="I29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J29" s="3">
         <v>-600</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K29" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M29" s="3"/>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N29" s="3"/>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1410,9 +1473,12 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-      <c r="M30" s="3"/>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3"/>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1443,75 +1509,84 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-      <c r="M31" s="3"/>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3"/>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-15100</v>
+        <v>-2800</v>
       </c>
       <c r="E32" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="F32" s="3">
         <v>-8000</v>
       </c>
-      <c r="F32" s="3">
-        <v>-4900</v>
-      </c>
       <c r="G32" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="H32" s="3">
         <v>-6700</v>
       </c>
-      <c r="H32" s="3">
-        <v>-4000</v>
-      </c>
       <c r="I32" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="J32" s="3">
         <v>-1400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M32" s="3"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-40100</v>
+        <v>-29300</v>
       </c>
       <c r="E33" s="3">
-        <v>19200</v>
+        <v>-39800</v>
       </c>
       <c r="F33" s="3">
-        <v>31800</v>
+        <v>19000</v>
       </c>
       <c r="G33" s="3">
-        <v>79600</v>
+        <v>31600</v>
       </c>
       <c r="H33" s="3">
-        <v>15800</v>
+        <v>79100</v>
       </c>
       <c r="I33" s="3">
+        <v>15700</v>
+      </c>
+      <c r="J33" s="3">
         <v>6400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-8800</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M33" s="3"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N33" s="3"/>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1542,80 +1617,89 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-      <c r="M34" s="3"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3"/>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-40100</v>
+        <v>-29300</v>
       </c>
       <c r="E35" s="3">
-        <v>19200</v>
+        <v>-39800</v>
       </c>
       <c r="F35" s="3">
-        <v>31800</v>
+        <v>19000</v>
       </c>
       <c r="G35" s="3">
-        <v>79600</v>
+        <v>31600</v>
       </c>
       <c r="H35" s="3">
-        <v>15800</v>
+        <v>79100</v>
       </c>
       <c r="I35" s="3">
+        <v>15700</v>
+      </c>
+      <c r="J35" s="3">
         <v>6400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-8800</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M35" s="3"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N35" s="3"/>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M38" s="2"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N38" s="2"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1629,8 +1713,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1644,305 +1729,333 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>123300</v>
+        <v>131100</v>
       </c>
       <c r="E41" s="3">
-        <v>204800</v>
+        <v>122500</v>
       </c>
       <c r="F41" s="3">
-        <v>316700</v>
+        <v>203600</v>
       </c>
       <c r="G41" s="3">
-        <v>250700</v>
+        <v>314800</v>
       </c>
       <c r="H41" s="3">
-        <v>213900</v>
+        <v>249100</v>
       </c>
       <c r="I41" s="3">
-        <v>50900</v>
+        <v>212600</v>
       </c>
       <c r="J41" s="3">
+        <v>50600</v>
+      </c>
+      <c r="K41" s="3">
         <v>21300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>31600</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M41" s="3"/>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N41" s="3"/>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>4800</v>
+        <v>5100</v>
       </c>
       <c r="E42" s="3">
+        <v>4700</v>
+      </c>
+      <c r="F42" s="3">
         <v>2700</v>
       </c>
-      <c r="F42" s="3">
-        <v>2600</v>
-      </c>
       <c r="G42" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H42" s="3">
         <v>2400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>7000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1300</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M42" s="3"/>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N42" s="3"/>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>121000</v>
+        <v>80400</v>
       </c>
       <c r="E43" s="3">
-        <v>151200</v>
+        <v>120200</v>
       </c>
       <c r="F43" s="3">
-        <v>177900</v>
+        <v>150300</v>
       </c>
       <c r="G43" s="3">
-        <v>231300</v>
+        <v>176800</v>
       </c>
       <c r="H43" s="3">
-        <v>105300</v>
+        <v>229900</v>
       </c>
       <c r="I43" s="3">
-        <v>89100</v>
+        <v>104700</v>
       </c>
       <c r="J43" s="3">
+        <v>88600</v>
+      </c>
+      <c r="K43" s="3">
         <v>69300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>29500</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M43" s="3"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N43" s="3"/>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>142100</v>
+        <v>83300</v>
       </c>
       <c r="E44" s="3">
-        <v>173700</v>
+        <v>141200</v>
       </c>
       <c r="F44" s="3">
-        <v>169300</v>
+        <v>172600</v>
       </c>
       <c r="G44" s="3">
-        <v>124300</v>
+        <v>168200</v>
       </c>
       <c r="H44" s="3">
-        <v>67400</v>
+        <v>123500</v>
       </c>
       <c r="I44" s="3">
-        <v>34700</v>
+        <v>67000</v>
       </c>
       <c r="J44" s="3">
+        <v>34500</v>
+      </c>
+      <c r="K44" s="3">
         <v>26700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>12900</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M44" s="3"/>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N44" s="3"/>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>20200</v>
+        <v>10800</v>
       </c>
       <c r="E45" s="3">
-        <v>14000</v>
+        <v>20100</v>
       </c>
       <c r="F45" s="3">
-        <v>4700</v>
+        <v>13900</v>
       </c>
       <c r="G45" s="3">
+        <v>4600</v>
+      </c>
+      <c r="H45" s="3">
         <v>2000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>600</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M45" s="3"/>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3"/>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>411300</v>
+        <v>310700</v>
       </c>
       <c r="E46" s="3">
-        <v>546500</v>
+        <v>408800</v>
       </c>
       <c r="F46" s="3">
-        <v>671200</v>
+        <v>543100</v>
       </c>
       <c r="G46" s="3">
-        <v>610600</v>
+        <v>667000</v>
       </c>
       <c r="H46" s="3">
-        <v>397200</v>
+        <v>606900</v>
       </c>
       <c r="I46" s="3">
-        <v>180100</v>
+        <v>394800</v>
       </c>
       <c r="J46" s="3">
+        <v>179000</v>
+      </c>
+      <c r="K46" s="3">
         <v>119500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>74600</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M46" s="3"/>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N46" s="3"/>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>235400</v>
+        <v>236900</v>
       </c>
       <c r="E47" s="3">
-        <v>215800</v>
+        <v>233900</v>
       </c>
       <c r="F47" s="3">
-        <v>61700</v>
+        <v>214500</v>
       </c>
       <c r="G47" s="3">
-        <v>56500</v>
+        <v>61300</v>
       </c>
       <c r="H47" s="3">
-        <v>29000</v>
+        <v>56100</v>
       </c>
       <c r="I47" s="3">
+        <v>28900</v>
+      </c>
+      <c r="J47" s="3">
         <v>11800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>10900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>300</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M47" s="3"/>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3"/>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>23100</v>
+        <v>15400</v>
       </c>
       <c r="E48" s="3">
-        <v>33700</v>
+        <v>23000</v>
       </c>
       <c r="F48" s="3">
-        <v>38300</v>
+        <v>33500</v>
       </c>
       <c r="G48" s="3">
-        <v>24100</v>
+        <v>38100</v>
       </c>
       <c r="H48" s="3">
-        <v>5600</v>
+        <v>23900</v>
       </c>
       <c r="I48" s="3">
+        <v>5500</v>
+      </c>
+      <c r="J48" s="3">
         <v>4000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>400</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M48" s="3"/>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N48" s="3"/>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>26300</v>
+        <v>19100</v>
       </c>
       <c r="E49" s="3">
-        <v>27300</v>
+        <v>26200</v>
       </c>
       <c r="F49" s="3">
-        <v>28900</v>
+        <v>27200</v>
       </c>
       <c r="G49" s="3">
+        <v>28700</v>
+      </c>
+      <c r="H49" s="3">
         <v>12700</v>
       </c>
-      <c r="H49" s="3">
-        <v>9700</v>
-      </c>
       <c r="I49" s="3">
+        <v>9600</v>
+      </c>
+      <c r="J49" s="3">
         <v>1600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>200</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M49" s="3"/>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N49" s="3"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1973,9 +2086,12 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-      <c r="M50" s="3"/>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3"/>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2006,42 +2122,48 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-      <c r="M51" s="3"/>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3"/>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>36200</v>
+        <v>41300</v>
       </c>
       <c r="E52" s="3">
-        <v>22700</v>
+        <v>36000</v>
       </c>
       <c r="F52" s="3">
-        <v>20600</v>
+        <v>22500</v>
       </c>
       <c r="G52" s="3">
-        <v>15500</v>
+        <v>20500</v>
       </c>
       <c r="H52" s="3">
-        <v>11500</v>
+        <v>15400</v>
       </c>
       <c r="I52" s="3">
+        <v>11400</v>
+      </c>
+      <c r="J52" s="3">
         <v>6200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>600</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M52" s="3"/>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N52" s="3"/>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2072,42 +2194,48 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-      <c r="M53" s="3"/>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3"/>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>732300</v>
+        <v>623400</v>
       </c>
       <c r="E54" s="3">
-        <v>846000</v>
+        <v>727800</v>
       </c>
       <c r="F54" s="3">
-        <v>820700</v>
+        <v>840800</v>
       </c>
       <c r="G54" s="3">
-        <v>719400</v>
+        <v>815700</v>
       </c>
       <c r="H54" s="3">
-        <v>453000</v>
+        <v>714900</v>
       </c>
       <c r="I54" s="3">
-        <v>203700</v>
+        <v>450200</v>
       </c>
       <c r="J54" s="3">
+        <v>202500</v>
+      </c>
+      <c r="K54" s="3">
         <v>135300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>76000</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M54" s="3"/>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N54" s="3"/>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2121,8 +2249,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2136,155 +2265,168 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>69200</v>
+        <v>40000</v>
       </c>
       <c r="E57" s="3">
-        <v>190100</v>
+        <v>68700</v>
       </c>
       <c r="F57" s="3">
-        <v>272800</v>
+        <v>188900</v>
       </c>
       <c r="G57" s="3">
-        <v>280100</v>
+        <v>271100</v>
       </c>
       <c r="H57" s="3">
-        <v>149400</v>
+        <v>278400</v>
       </c>
       <c r="I57" s="3">
-        <v>99500</v>
+        <v>148500</v>
       </c>
       <c r="J57" s="3">
+        <v>98900</v>
+      </c>
+      <c r="K57" s="3">
         <v>76100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>37300</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M57" s="3"/>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N57" s="3"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>134600</v>
+        <v>67400</v>
       </c>
       <c r="E58" s="3">
-        <v>64200</v>
+        <v>133800</v>
       </c>
       <c r="F58" s="3">
-        <v>70200</v>
+        <v>63800</v>
       </c>
       <c r="G58" s="3">
+        <v>69700</v>
+      </c>
+      <c r="H58" s="3">
         <v>300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1800</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M58" s="3"/>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N58" s="3"/>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>28200</v>
+        <v>44800</v>
       </c>
       <c r="E59" s="3">
-        <v>44900</v>
+        <v>28000</v>
       </c>
       <c r="F59" s="3">
-        <v>44800</v>
+        <v>44600</v>
       </c>
       <c r="G59" s="3">
-        <v>64600</v>
+        <v>44600</v>
       </c>
       <c r="H59" s="3">
-        <v>38100</v>
+        <v>64200</v>
       </c>
       <c r="I59" s="3">
-        <v>17500</v>
+        <v>37800</v>
       </c>
       <c r="J59" s="3">
+        <v>17400</v>
+      </c>
+      <c r="K59" s="3">
         <v>10300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2600</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M59" s="3"/>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3"/>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>232000</v>
+        <v>152200</v>
       </c>
       <c r="E60" s="3">
-        <v>299200</v>
+        <v>230500</v>
       </c>
       <c r="F60" s="3">
-        <v>387800</v>
+        <v>297300</v>
       </c>
       <c r="G60" s="3">
-        <v>345000</v>
+        <v>385400</v>
       </c>
       <c r="H60" s="3">
-        <v>192900</v>
+        <v>342900</v>
       </c>
       <c r="I60" s="3">
-        <v>122000</v>
+        <v>191700</v>
       </c>
       <c r="J60" s="3">
+        <v>121200</v>
+      </c>
+      <c r="K60" s="3">
         <v>88200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>39900</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M60" s="3"/>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N60" s="3"/>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>95100</v>
+        <v>117700</v>
       </c>
       <c r="E61" s="3">
-        <v>101000</v>
+        <v>94500</v>
       </c>
       <c r="F61" s="3">
+        <v>100400</v>
+      </c>
+      <c r="G61" s="3">
         <v>8300</v>
       </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
       <c r="H61" s="3">
         <v>0</v>
       </c>
@@ -2300,42 +2442,48 @@
       <c r="L61" s="3">
         <v>0</v>
       </c>
-      <c r="M61" s="3"/>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3"/>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>32000</v>
+        <v>7500</v>
       </c>
       <c r="E62" s="3">
-        <v>38000</v>
+        <v>31800</v>
       </c>
       <c r="F62" s="3">
-        <v>45000</v>
+        <v>37700</v>
       </c>
       <c r="G62" s="3">
-        <v>27200</v>
+        <v>44700</v>
       </c>
       <c r="H62" s="3">
+        <v>27000</v>
+      </c>
+      <c r="I62" s="3">
         <v>8500</v>
       </c>
-      <c r="I62" s="3">
-        <v>1500</v>
-      </c>
       <c r="J62" s="3">
-        <v>0</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
+        <v>1400</v>
+      </c>
+      <c r="K62" s="3">
+        <v>0</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3"/>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3"/>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2366,9 +2514,12 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-      <c r="M63" s="3"/>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2399,9 +2550,12 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-      <c r="M64" s="3"/>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3"/>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2432,42 +2586,48 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-      <c r="M65" s="3"/>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3"/>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>360800</v>
+        <v>279000</v>
       </c>
       <c r="E66" s="3">
-        <v>440000</v>
+        <v>358500</v>
       </c>
       <c r="F66" s="3">
-        <v>441200</v>
+        <v>437300</v>
       </c>
       <c r="G66" s="3">
-        <v>371700</v>
+        <v>438400</v>
       </c>
       <c r="H66" s="3">
-        <v>201200</v>
+        <v>369400</v>
       </c>
       <c r="I66" s="3">
-        <v>123700</v>
+        <v>200000</v>
       </c>
       <c r="J66" s="3">
+        <v>123000</v>
+      </c>
+      <c r="K66" s="3">
         <v>88200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>39900</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M66" s="3"/>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N66" s="3"/>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2481,8 +2641,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2513,9 +2674,12 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-      <c r="M68" s="3"/>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3"/>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2546,9 +2710,12 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-      <c r="M69" s="3"/>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3"/>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2568,20 +2735,23 @@
         <v>0</v>
       </c>
       <c r="I70" s="3">
-        <v>48600</v>
+        <v>0</v>
       </c>
       <c r="J70" s="3">
+        <v>48300</v>
+      </c>
+      <c r="K70" s="3">
         <v>42900</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>39100</v>
       </c>
-      <c r="L70" s="3">
-        <v>0</v>
-      </c>
-      <c r="M70" s="3"/>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3"/>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2612,42 +2782,48 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-      <c r="M71" s="3"/>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3"/>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>131100</v>
+        <v>101000</v>
       </c>
       <c r="E72" s="3">
-        <v>176700</v>
+        <v>130300</v>
       </c>
       <c r="F72" s="3">
-        <v>157600</v>
+        <v>175600</v>
       </c>
       <c r="G72" s="3">
-        <v>126600</v>
+        <v>156600</v>
       </c>
       <c r="H72" s="3">
-        <v>47300</v>
+        <v>125800</v>
       </c>
       <c r="I72" s="3">
-        <v>18200</v>
+        <v>47000</v>
       </c>
       <c r="J72" s="3">
+        <v>18100</v>
+      </c>
+      <c r="K72" s="3">
         <v>-5100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-8700</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M72" s="3"/>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N72" s="3"/>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2678,9 +2854,12 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-      <c r="M73" s="3"/>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3"/>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2711,9 +2890,12 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-      <c r="M74" s="3"/>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3"/>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2744,42 +2926,48 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-      <c r="M75" s="3"/>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3"/>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>371500</v>
+        <v>344400</v>
       </c>
       <c r="E76" s="3">
-        <v>406000</v>
+        <v>369200</v>
       </c>
       <c r="F76" s="3">
-        <v>379600</v>
+        <v>403500</v>
       </c>
       <c r="G76" s="3">
-        <v>347700</v>
+        <v>377200</v>
       </c>
       <c r="H76" s="3">
-        <v>251800</v>
+        <v>345500</v>
       </c>
       <c r="I76" s="3">
-        <v>31400</v>
+        <v>250200</v>
       </c>
       <c r="J76" s="3">
+        <v>31200</v>
+      </c>
+      <c r="K76" s="3">
         <v>4200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-3000</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M76" s="3"/>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N76" s="3"/>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2810,80 +2998,89 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-      <c r="M77" s="3"/>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3"/>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M80" s="2"/>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N80" s="2"/>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-40100</v>
+        <v>-29300</v>
       </c>
       <c r="E81" s="3">
-        <v>19200</v>
+        <v>-39800</v>
       </c>
       <c r="F81" s="3">
-        <v>31800</v>
+        <v>19000</v>
       </c>
       <c r="G81" s="3">
-        <v>79600</v>
+        <v>31600</v>
       </c>
       <c r="H81" s="3">
-        <v>15800</v>
+        <v>79100</v>
       </c>
       <c r="I81" s="3">
+        <v>15700</v>
+      </c>
+      <c r="J81" s="3">
         <v>6400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-8800</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M81" s="3"/>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N81" s="3"/>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2897,41 +3094,45 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E83" s="3">
         <v>8100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>7200</v>
       </c>
-      <c r="F83" s="3">
-        <v>3800</v>
-      </c>
       <c r="G83" s="3">
+        <v>3700</v>
+      </c>
+      <c r="H83" s="3">
         <v>2400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>300</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M83" s="3"/>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3"/>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2962,9 +3163,12 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-      <c r="M84" s="3"/>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3"/>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2995,9 +3199,12 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-      <c r="M85" s="3"/>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3"/>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3028,9 +3235,12 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-      <c r="M86" s="3"/>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3"/>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3061,9 +3271,12 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-      <c r="M87" s="3"/>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3"/>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3094,42 +3307,48 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-      <c r="M88" s="3"/>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3"/>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-109500</v>
+        <v>41300</v>
       </c>
       <c r="E89" s="3">
-        <v>-32300</v>
+        <v>-108800</v>
       </c>
       <c r="F89" s="3">
-        <v>21900</v>
+        <v>-32100</v>
       </c>
       <c r="G89" s="3">
-        <v>59500</v>
+        <v>21700</v>
       </c>
       <c r="H89" s="3">
-        <v>98400</v>
+        <v>59100</v>
       </c>
       <c r="I89" s="3">
-        <v>33100</v>
+        <v>97800</v>
       </c>
       <c r="J89" s="3">
+        <v>32900</v>
+      </c>
+      <c r="K89" s="3">
         <v>2400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1000</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M89" s="3"/>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3"/>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3143,41 +3362,45 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-6400</v>
       </c>
-      <c r="F91" s="3">
-        <v>-11600</v>
-      </c>
       <c r="G91" s="3">
-        <v>-4800</v>
+        <v>-11500</v>
       </c>
       <c r="H91" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="I91" s="3">
         <v>-2400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-400</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M91" s="3"/>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N91" s="3"/>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3208,9 +3431,12 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-      <c r="M92" s="3"/>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3"/>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3241,42 +3467,48 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-      <c r="M93" s="3"/>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3"/>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-5900</v>
+        <v>7600</v>
       </c>
       <c r="E94" s="3">
-        <v>-148700</v>
+        <v>-5800</v>
       </c>
       <c r="F94" s="3">
-        <v>-28800</v>
+        <v>-147700</v>
       </c>
       <c r="G94" s="3">
-        <v>-15700</v>
+        <v>-28600</v>
       </c>
       <c r="H94" s="3">
-        <v>-45200</v>
+        <v>-15600</v>
       </c>
       <c r="I94" s="3">
+        <v>-44900</v>
+      </c>
+      <c r="J94" s="3">
         <v>-5400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-13800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-700</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M94" s="3"/>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3"/>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3290,16 +3522,17 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-5600</v>
+        <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>-5500</v>
       </c>
       <c r="F96" s="3">
         <v>0</v>
@@ -3322,9 +3555,12 @@
       <c r="L96" s="3">
         <v>0</v>
       </c>
-      <c r="M96" s="3"/>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3"/>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3355,9 +3591,12 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-      <c r="M97" s="3"/>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3"/>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3388,9 +3627,12 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-      <c r="M98" s="3"/>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3"/>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3421,106 +3663,118 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-      <c r="M99" s="3"/>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3"/>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>40200</v>
+        <v>-40800</v>
       </c>
       <c r="E100" s="3">
-        <v>76600</v>
+        <v>40000</v>
       </c>
       <c r="F100" s="3">
-        <v>78500</v>
+        <v>76100</v>
       </c>
       <c r="G100" s="3">
-        <v>3600</v>
+        <v>78000</v>
       </c>
       <c r="H100" s="3">
-        <v>88900</v>
+        <v>3500</v>
       </c>
       <c r="I100" s="3">
+        <v>88300</v>
+      </c>
+      <c r="J100" s="3">
         <v>2800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>30700</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M100" s="3"/>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3"/>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E101" s="3">
         <v>600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-2200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-6000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1600</v>
       </c>
-      <c r="H101" s="3">
-        <v>8400</v>
-      </c>
       <c r="I101" s="3">
+        <v>8300</v>
+      </c>
+      <c r="J101" s="3">
         <v>-400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1500</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M101" s="3"/>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N101" s="3"/>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-74500</v>
+        <v>3300</v>
       </c>
       <c r="E102" s="3">
-        <v>-106500</v>
+        <v>-74100</v>
       </c>
       <c r="F102" s="3">
-        <v>65600</v>
+        <v>-105900</v>
       </c>
       <c r="G102" s="3">
-        <v>49000</v>
+        <v>65200</v>
       </c>
       <c r="H102" s="3">
-        <v>150500</v>
+        <v>48700</v>
       </c>
       <c r="I102" s="3">
-        <v>30100</v>
+        <v>149500</v>
       </c>
       <c r="J102" s="3">
+        <v>29900</v>
+      </c>
+      <c r="K102" s="3">
         <v>-9300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>30500</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M102" s="3"/>
+      <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/ZEPP_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ZEPP_YR_FIN.xlsx
@@ -718,25 +718,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>344800</v>
+        <v>2495300</v>
       </c>
       <c r="E8" s="3">
-        <v>572400</v>
+        <v>4142900</v>
       </c>
       <c r="F8" s="3">
-        <v>863500</v>
+        <v>6250100</v>
       </c>
       <c r="G8" s="3">
-        <v>888800</v>
+        <v>6433400</v>
       </c>
       <c r="H8" s="3">
-        <v>803000</v>
+        <v>5812300</v>
       </c>
       <c r="I8" s="3">
-        <v>503600</v>
+        <v>3645300</v>
       </c>
       <c r="J8" s="3">
-        <v>283100</v>
+        <v>2048900</v>
       </c>
       <c r="K8" s="3">
         <v>216400</v>
@@ -754,25 +754,25 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>253900</v>
+        <v>1837500</v>
       </c>
       <c r="E9" s="3">
-        <v>461400</v>
+        <v>3339700</v>
       </c>
       <c r="F9" s="3">
-        <v>683100</v>
+        <v>4944500</v>
       </c>
       <c r="G9" s="3">
-        <v>704700</v>
+        <v>5100700</v>
       </c>
       <c r="H9" s="3">
-        <v>600200</v>
+        <v>4344500</v>
       </c>
       <c r="I9" s="3">
-        <v>373800</v>
+        <v>2705900</v>
       </c>
       <c r="J9" s="3">
-        <v>214700</v>
+        <v>1554200</v>
       </c>
       <c r="K9" s="3">
         <v>178000</v>
@@ -790,25 +790,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>90900</v>
+        <v>657800</v>
       </c>
       <c r="E10" s="3">
-        <v>111000</v>
+        <v>803100</v>
       </c>
       <c r="F10" s="3">
-        <v>180400</v>
+        <v>1305600</v>
       </c>
       <c r="G10" s="3">
-        <v>184100</v>
+        <v>1332700</v>
       </c>
       <c r="H10" s="3">
-        <v>202800</v>
+        <v>1467700</v>
       </c>
       <c r="I10" s="3">
-        <v>129800</v>
+        <v>939500</v>
       </c>
       <c r="J10" s="3">
-        <v>68300</v>
+        <v>494700</v>
       </c>
       <c r="K10" s="3">
         <v>38400</v>
@@ -842,25 +842,25 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>50000</v>
+        <v>361800</v>
       </c>
       <c r="E12" s="3">
-        <v>71400</v>
+        <v>517100</v>
       </c>
       <c r="F12" s="3">
-        <v>71200</v>
+        <v>515100</v>
       </c>
       <c r="G12" s="3">
-        <v>74300</v>
+        <v>538000</v>
       </c>
       <c r="H12" s="3">
-        <v>59500</v>
+        <v>430800</v>
       </c>
       <c r="I12" s="3">
-        <v>36400</v>
+        <v>263200</v>
       </c>
       <c r="J12" s="3">
-        <v>21300</v>
+        <v>153800</v>
       </c>
       <c r="K12" s="3">
         <v>18400</v>
@@ -914,22 +914,22 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>300</v>
+        <v>2300</v>
       </c>
       <c r="E14" s="3">
-        <v>1900</v>
+        <v>13900</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
       </c>
       <c r="G14" s="3">
-        <v>-7800</v>
+        <v>-56500</v>
       </c>
       <c r="H14" s="3">
-        <v>400</v>
+        <v>2600</v>
       </c>
       <c r="I14" s="3">
-        <v>1000</v>
+        <v>7600</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
@@ -999,25 +999,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>373700</v>
+        <v>2704700</v>
       </c>
       <c r="E17" s="3">
-        <v>631000</v>
+        <v>4567000</v>
       </c>
       <c r="F17" s="3">
-        <v>850500</v>
+        <v>6156200</v>
       </c>
       <c r="G17" s="3">
-        <v>857000</v>
+        <v>6202600</v>
       </c>
       <c r="H17" s="3">
-        <v>719600</v>
+        <v>5208400</v>
       </c>
       <c r="I17" s="3">
-        <v>454200</v>
+        <v>3287200</v>
       </c>
       <c r="J17" s="3">
-        <v>257900</v>
+        <v>1866900</v>
       </c>
       <c r="K17" s="3">
         <v>214500</v>
@@ -1035,25 +1035,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-28900</v>
+        <v>-209400</v>
       </c>
       <c r="E18" s="3">
-        <v>-58600</v>
+        <v>-424100</v>
       </c>
       <c r="F18" s="3">
-        <v>13000</v>
+        <v>93900</v>
       </c>
       <c r="G18" s="3">
-        <v>31900</v>
+        <v>230700</v>
       </c>
       <c r="H18" s="3">
-        <v>83400</v>
+        <v>603900</v>
       </c>
       <c r="I18" s="3">
-        <v>49500</v>
+        <v>358100</v>
       </c>
       <c r="J18" s="3">
-        <v>25100</v>
+        <v>182000</v>
       </c>
       <c r="K18" s="3">
         <v>1900</v>
@@ -1087,25 +1087,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>2800</v>
+        <v>20300</v>
       </c>
       <c r="E20" s="3">
-        <v>15000</v>
+        <v>108600</v>
       </c>
       <c r="F20" s="3">
-        <v>8000</v>
+        <v>57600</v>
       </c>
       <c r="G20" s="3">
-        <v>4800</v>
+        <v>34900</v>
       </c>
       <c r="H20" s="3">
-        <v>6700</v>
+        <v>48500</v>
       </c>
       <c r="I20" s="3">
-        <v>3900</v>
+        <v>28500</v>
       </c>
       <c r="J20" s="3">
-        <v>1400</v>
+        <v>9900</v>
       </c>
       <c r="K20" s="3">
         <v>2200</v>
@@ -1123,25 +1123,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-18600</v>
+        <v>-134600</v>
       </c>
       <c r="E21" s="3">
-        <v>-35500</v>
+        <v>-256900</v>
       </c>
       <c r="F21" s="3">
-        <v>28100</v>
+        <v>203400</v>
       </c>
       <c r="G21" s="3">
-        <v>40400</v>
+        <v>292700</v>
       </c>
       <c r="H21" s="3">
-        <v>92500</v>
+        <v>669600</v>
       </c>
       <c r="I21" s="3">
-        <v>54300</v>
+        <v>392800</v>
       </c>
       <c r="J21" s="3">
-        <v>27000</v>
+        <v>195600</v>
       </c>
       <c r="K21" s="3">
         <v>4300</v>
@@ -1159,13 +1159,13 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>6600</v>
+        <v>47700</v>
       </c>
       <c r="E22" s="3">
-        <v>7900</v>
+        <v>57000</v>
       </c>
       <c r="F22" s="3">
-        <v>6200</v>
+        <v>44900</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>3</v>
@@ -1195,25 +1195,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-32700</v>
+        <v>-236800</v>
       </c>
       <c r="E23" s="3">
-        <v>-51500</v>
+        <v>-372500</v>
       </c>
       <c r="F23" s="3">
-        <v>14700</v>
+        <v>106700</v>
       </c>
       <c r="G23" s="3">
-        <v>36700</v>
+        <v>265600</v>
       </c>
       <c r="H23" s="3">
-        <v>90100</v>
+        <v>652400</v>
       </c>
       <c r="I23" s="3">
-        <v>53400</v>
+        <v>386600</v>
       </c>
       <c r="J23" s="3">
-        <v>26500</v>
+        <v>191900</v>
       </c>
       <c r="K23" s="3">
         <v>4000</v>
@@ -1231,25 +1231,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-2200</v>
+        <v>-15800</v>
       </c>
       <c r="E24" s="3">
-        <v>-9100</v>
+        <v>-65900</v>
       </c>
       <c r="F24" s="3">
-        <v>1500</v>
+        <v>10700</v>
       </c>
       <c r="G24" s="3">
-        <v>4300</v>
+        <v>31200</v>
       </c>
       <c r="H24" s="3">
-        <v>10800</v>
+        <v>77900</v>
       </c>
       <c r="I24" s="3">
-        <v>7200</v>
+        <v>52000</v>
       </c>
       <c r="J24" s="3">
-        <v>3200</v>
+        <v>23400</v>
       </c>
       <c r="K24" s="3">
         <v>400</v>
@@ -1303,25 +1303,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-30500</v>
+        <v>-221000</v>
       </c>
       <c r="E26" s="3">
-        <v>-42400</v>
+        <v>-306700</v>
       </c>
       <c r="F26" s="3">
-        <v>13300</v>
+        <v>95900</v>
       </c>
       <c r="G26" s="3">
-        <v>32400</v>
+        <v>234500</v>
       </c>
       <c r="H26" s="3">
-        <v>79400</v>
+        <v>574500</v>
       </c>
       <c r="I26" s="3">
-        <v>46200</v>
+        <v>334600</v>
       </c>
       <c r="J26" s="3">
-        <v>23300</v>
+        <v>168500</v>
       </c>
       <c r="K26" s="3">
         <v>3600</v>
@@ -1339,25 +1339,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-29300</v>
+        <v>-212100</v>
       </c>
       <c r="E27" s="3">
-        <v>-39800</v>
+        <v>-288300</v>
       </c>
       <c r="F27" s="3">
-        <v>19000</v>
+        <v>137800</v>
       </c>
       <c r="G27" s="3">
-        <v>31600</v>
+        <v>228800</v>
       </c>
       <c r="H27" s="3">
-        <v>79100</v>
+        <v>572700</v>
       </c>
       <c r="I27" s="3">
-        <v>15700</v>
+        <v>113500</v>
       </c>
       <c r="J27" s="3">
-        <v>7000</v>
+        <v>50300</v>
       </c>
       <c r="K27" s="3">
         <v>-1700</v>
@@ -1429,7 +1429,7 @@
         <v>3</v>
       </c>
       <c r="J29" s="3">
-        <v>-600</v>
+        <v>-4200</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>3</v>
@@ -1519,25 +1519,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-2800</v>
+        <v>-20300</v>
       </c>
       <c r="E32" s="3">
-        <v>-15000</v>
+        <v>-108600</v>
       </c>
       <c r="F32" s="3">
-        <v>-8000</v>
+        <v>-57600</v>
       </c>
       <c r="G32" s="3">
-        <v>-4800</v>
+        <v>-34900</v>
       </c>
       <c r="H32" s="3">
-        <v>-6700</v>
+        <v>-48500</v>
       </c>
       <c r="I32" s="3">
-        <v>-3900</v>
+        <v>-28500</v>
       </c>
       <c r="J32" s="3">
-        <v>-1400</v>
+        <v>-9900</v>
       </c>
       <c r="K32" s="3">
         <v>-2200</v>
@@ -1555,25 +1555,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-29300</v>
+        <v>-212100</v>
       </c>
       <c r="E33" s="3">
-        <v>-39800</v>
+        <v>-288300</v>
       </c>
       <c r="F33" s="3">
-        <v>19000</v>
+        <v>137800</v>
       </c>
       <c r="G33" s="3">
-        <v>31600</v>
+        <v>228800</v>
       </c>
       <c r="H33" s="3">
-        <v>79100</v>
+        <v>572700</v>
       </c>
       <c r="I33" s="3">
-        <v>15700</v>
+        <v>113500</v>
       </c>
       <c r="J33" s="3">
-        <v>6400</v>
+        <v>46100</v>
       </c>
       <c r="K33" s="3">
         <v>-1700</v>
@@ -1627,25 +1627,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-29300</v>
+        <v>-212100</v>
       </c>
       <c r="E35" s="3">
-        <v>-39800</v>
+        <v>-288300</v>
       </c>
       <c r="F35" s="3">
-        <v>19000</v>
+        <v>137800</v>
       </c>
       <c r="G35" s="3">
-        <v>31600</v>
+        <v>228800</v>
       </c>
       <c r="H35" s="3">
-        <v>79100</v>
+        <v>572700</v>
       </c>
       <c r="I35" s="3">
-        <v>15700</v>
+        <v>113500</v>
       </c>
       <c r="J35" s="3">
-        <v>6400</v>
+        <v>46100</v>
       </c>
       <c r="K35" s="3">
         <v>-1700</v>
@@ -1736,25 +1736,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>131100</v>
+        <v>133700</v>
       </c>
       <c r="E41" s="3">
-        <v>122500</v>
+        <v>886600</v>
       </c>
       <c r="F41" s="3">
-        <v>203600</v>
+        <v>1473500</v>
       </c>
       <c r="G41" s="3">
-        <v>314800</v>
+        <v>2278300</v>
       </c>
       <c r="H41" s="3">
-        <v>249100</v>
+        <v>1803100</v>
       </c>
       <c r="I41" s="3">
-        <v>212600</v>
+        <v>1538800</v>
       </c>
       <c r="J41" s="3">
-        <v>50600</v>
+        <v>366300</v>
       </c>
       <c r="K41" s="3">
         <v>21300</v>
@@ -1772,25 +1772,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>5100</v>
+        <v>5200</v>
       </c>
       <c r="E42" s="3">
-        <v>4700</v>
+        <v>34300</v>
       </c>
       <c r="F42" s="3">
-        <v>2700</v>
+        <v>19400</v>
       </c>
       <c r="G42" s="3">
-        <v>2500</v>
+        <v>18400</v>
       </c>
       <c r="H42" s="3">
-        <v>2400</v>
+        <v>17200</v>
       </c>
       <c r="I42" s="3">
-        <v>7000</v>
+        <v>50500</v>
       </c>
       <c r="J42" s="3">
-        <v>1900</v>
+        <v>13700</v>
       </c>
       <c r="K42" s="3">
         <v>1300</v>
@@ -1808,25 +1808,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>80400</v>
+        <v>590200</v>
       </c>
       <c r="E43" s="3">
-        <v>120200</v>
+        <v>870300</v>
       </c>
       <c r="F43" s="3">
-        <v>150300</v>
+        <v>1087900</v>
       </c>
       <c r="G43" s="3">
-        <v>176800</v>
+        <v>1280000</v>
       </c>
       <c r="H43" s="3">
-        <v>229900</v>
+        <v>1664000</v>
       </c>
       <c r="I43" s="3">
-        <v>104700</v>
+        <v>757500</v>
       </c>
       <c r="J43" s="3">
-        <v>88600</v>
+        <v>641000</v>
       </c>
       <c r="K43" s="3">
         <v>69300</v>
@@ -1844,25 +1844,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>83300</v>
+        <v>687600</v>
       </c>
       <c r="E44" s="3">
-        <v>141200</v>
+        <v>1021900</v>
       </c>
       <c r="F44" s="3">
-        <v>172600</v>
+        <v>1249300</v>
       </c>
       <c r="G44" s="3">
-        <v>168200</v>
+        <v>1217500</v>
       </c>
       <c r="H44" s="3">
-        <v>123500</v>
+        <v>893800</v>
       </c>
       <c r="I44" s="3">
-        <v>67000</v>
+        <v>484600</v>
       </c>
       <c r="J44" s="3">
-        <v>34500</v>
+        <v>249700</v>
       </c>
       <c r="K44" s="3">
         <v>26700</v>
@@ -1880,25 +1880,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>10800</v>
+        <v>53900</v>
       </c>
       <c r="E45" s="3">
-        <v>20100</v>
+        <v>145400</v>
       </c>
       <c r="F45" s="3">
-        <v>13900</v>
+        <v>100800</v>
       </c>
       <c r="G45" s="3">
-        <v>4600</v>
+        <v>33600</v>
       </c>
       <c r="H45" s="3">
-        <v>2000</v>
+        <v>14400</v>
       </c>
       <c r="I45" s="3">
-        <v>3600</v>
+        <v>26100</v>
       </c>
       <c r="J45" s="3">
-        <v>3400</v>
+        <v>24600</v>
       </c>
       <c r="K45" s="3">
         <v>900</v>
@@ -1916,25 +1916,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>310700</v>
+        <v>316700</v>
       </c>
       <c r="E46" s="3">
-        <v>408800</v>
+        <v>2958500</v>
       </c>
       <c r="F46" s="3">
-        <v>543100</v>
+        <v>3931000</v>
       </c>
       <c r="G46" s="3">
-        <v>667000</v>
+        <v>4827900</v>
       </c>
       <c r="H46" s="3">
-        <v>606900</v>
+        <v>4392500</v>
       </c>
       <c r="I46" s="3">
-        <v>394800</v>
+        <v>2857500</v>
       </c>
       <c r="J46" s="3">
-        <v>179000</v>
+        <v>1295400</v>
       </c>
       <c r="K46" s="3">
         <v>119500</v>
@@ -1952,25 +1952,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>236900</v>
+        <v>1935100</v>
       </c>
       <c r="E47" s="3">
-        <v>233900</v>
+        <v>1693000</v>
       </c>
       <c r="F47" s="3">
-        <v>214500</v>
+        <v>1552600</v>
       </c>
       <c r="G47" s="3">
-        <v>61300</v>
+        <v>444000</v>
       </c>
       <c r="H47" s="3">
-        <v>56100</v>
+        <v>406100</v>
       </c>
       <c r="I47" s="3">
-        <v>28900</v>
+        <v>208900</v>
       </c>
       <c r="J47" s="3">
-        <v>11800</v>
+        <v>85200</v>
       </c>
       <c r="K47" s="3">
         <v>10900</v>
@@ -1988,25 +1988,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>15400</v>
+        <v>127600</v>
       </c>
       <c r="E48" s="3">
-        <v>23000</v>
+        <v>166200</v>
       </c>
       <c r="F48" s="3">
-        <v>33500</v>
+        <v>242300</v>
       </c>
       <c r="G48" s="3">
-        <v>38100</v>
+        <v>275800</v>
       </c>
       <c r="H48" s="3">
-        <v>23900</v>
+        <v>173000</v>
       </c>
       <c r="I48" s="3">
-        <v>5500</v>
+        <v>40000</v>
       </c>
       <c r="J48" s="3">
-        <v>4000</v>
+        <v>28800</v>
       </c>
       <c r="K48" s="3">
         <v>1500</v>
@@ -2024,25 +2024,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>19100</v>
+        <v>89500</v>
       </c>
       <c r="E49" s="3">
-        <v>26200</v>
+        <v>189400</v>
       </c>
       <c r="F49" s="3">
-        <v>27200</v>
+        <v>196600</v>
       </c>
       <c r="G49" s="3">
-        <v>28700</v>
+        <v>207700</v>
       </c>
       <c r="H49" s="3">
-        <v>12700</v>
+        <v>91700</v>
       </c>
       <c r="I49" s="3">
-        <v>9600</v>
+        <v>69700</v>
       </c>
       <c r="J49" s="3">
-        <v>1600</v>
+        <v>11300</v>
       </c>
       <c r="K49" s="3">
         <v>200</v>
@@ -2132,25 +2132,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>41300</v>
+        <v>42100</v>
       </c>
       <c r="E52" s="3">
-        <v>36000</v>
+        <v>260600</v>
       </c>
       <c r="F52" s="3">
-        <v>22500</v>
+        <v>163000</v>
       </c>
       <c r="G52" s="3">
-        <v>20500</v>
+        <v>148400</v>
       </c>
       <c r="H52" s="3">
-        <v>15400</v>
+        <v>111500</v>
       </c>
       <c r="I52" s="3">
-        <v>11400</v>
+        <v>82400</v>
       </c>
       <c r="J52" s="3">
-        <v>6200</v>
+        <v>44900</v>
       </c>
       <c r="K52" s="3">
         <v>3200</v>
@@ -2204,25 +2204,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>623400</v>
+        <v>635500</v>
       </c>
       <c r="E54" s="3">
-        <v>727800</v>
+        <v>5267600</v>
       </c>
       <c r="F54" s="3">
-        <v>840800</v>
+        <v>6085500</v>
       </c>
       <c r="G54" s="3">
-        <v>815700</v>
+        <v>5903700</v>
       </c>
       <c r="H54" s="3">
-        <v>714900</v>
+        <v>5174700</v>
       </c>
       <c r="I54" s="3">
-        <v>450200</v>
+        <v>3258500</v>
       </c>
       <c r="J54" s="3">
-        <v>202500</v>
+        <v>1465500</v>
       </c>
       <c r="K54" s="3">
         <v>135300</v>
@@ -2272,25 +2272,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>40000</v>
+        <v>40800</v>
       </c>
       <c r="E57" s="3">
-        <v>68700</v>
+        <v>497600</v>
       </c>
       <c r="F57" s="3">
-        <v>188900</v>
+        <v>1367400</v>
       </c>
       <c r="G57" s="3">
-        <v>271100</v>
+        <v>1962500</v>
       </c>
       <c r="H57" s="3">
-        <v>278400</v>
+        <v>2014700</v>
       </c>
       <c r="I57" s="3">
-        <v>148500</v>
+        <v>1074800</v>
       </c>
       <c r="J57" s="3">
-        <v>98900</v>
+        <v>715900</v>
       </c>
       <c r="K57" s="3">
         <v>76100</v>
@@ -2308,25 +2308,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>67400</v>
+        <v>68700</v>
       </c>
       <c r="E58" s="3">
-        <v>133800</v>
+        <v>968400</v>
       </c>
       <c r="F58" s="3">
-        <v>63800</v>
+        <v>461800</v>
       </c>
       <c r="G58" s="3">
-        <v>69700</v>
+        <v>504700</v>
       </c>
       <c r="H58" s="3">
-        <v>300</v>
+        <v>2200</v>
       </c>
       <c r="I58" s="3">
-        <v>5400</v>
+        <v>38900</v>
       </c>
       <c r="J58" s="3">
-        <v>4900</v>
+        <v>35200</v>
       </c>
       <c r="K58" s="3">
         <v>1800</v>
@@ -2344,25 +2344,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>44800</v>
+        <v>361300</v>
       </c>
       <c r="E59" s="3">
-        <v>28000</v>
+        <v>202700</v>
       </c>
       <c r="F59" s="3">
-        <v>44600</v>
+        <v>322900</v>
       </c>
       <c r="G59" s="3">
-        <v>44600</v>
+        <v>322500</v>
       </c>
       <c r="H59" s="3">
-        <v>64200</v>
+        <v>464900</v>
       </c>
       <c r="I59" s="3">
-        <v>37800</v>
+        <v>274000</v>
       </c>
       <c r="J59" s="3">
-        <v>17400</v>
+        <v>126100</v>
       </c>
       <c r="K59" s="3">
         <v>10300</v>
@@ -2380,25 +2380,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>152200</v>
+        <v>155100</v>
       </c>
       <c r="E60" s="3">
-        <v>230500</v>
+        <v>1668700</v>
       </c>
       <c r="F60" s="3">
-        <v>297300</v>
+        <v>2152100</v>
       </c>
       <c r="G60" s="3">
-        <v>385400</v>
+        <v>2789700</v>
       </c>
       <c r="H60" s="3">
-        <v>342900</v>
+        <v>2481800</v>
       </c>
       <c r="I60" s="3">
-        <v>191700</v>
+        <v>1387700</v>
       </c>
       <c r="J60" s="3">
-        <v>121200</v>
+        <v>877200</v>
       </c>
       <c r="K60" s="3">
         <v>88200</v>
@@ -2416,16 +2416,16 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>117700</v>
+        <v>120000</v>
       </c>
       <c r="E61" s="3">
-        <v>94500</v>
+        <v>684200</v>
       </c>
       <c r="F61" s="3">
-        <v>100400</v>
+        <v>726900</v>
       </c>
       <c r="G61" s="3">
-        <v>8300</v>
+        <v>60000</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -2452,25 +2452,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>7500</v>
+        <v>7600</v>
       </c>
       <c r="E62" s="3">
-        <v>31800</v>
+        <v>229800</v>
       </c>
       <c r="F62" s="3">
-        <v>37700</v>
+        <v>273100</v>
       </c>
       <c r="G62" s="3">
-        <v>44700</v>
+        <v>323800</v>
       </c>
       <c r="H62" s="3">
-        <v>27000</v>
+        <v>195400</v>
       </c>
       <c r="I62" s="3">
-        <v>8500</v>
+        <v>61200</v>
       </c>
       <c r="J62" s="3">
-        <v>1400</v>
+        <v>10500</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -2596,25 +2596,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>279000</v>
+        <v>284600</v>
       </c>
       <c r="E66" s="3">
-        <v>358500</v>
+        <v>2595100</v>
       </c>
       <c r="F66" s="3">
-        <v>437300</v>
+        <v>3165200</v>
       </c>
       <c r="G66" s="3">
-        <v>438400</v>
+        <v>3173500</v>
       </c>
       <c r="H66" s="3">
-        <v>369400</v>
+        <v>2674000</v>
       </c>
       <c r="I66" s="3">
-        <v>200000</v>
+        <v>1447600</v>
       </c>
       <c r="J66" s="3">
-        <v>123000</v>
+        <v>890100</v>
       </c>
       <c r="K66" s="3">
         <v>88200</v>
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="J70" s="3">
-        <v>48300</v>
+        <v>349600</v>
       </c>
       <c r="K70" s="3">
         <v>42900</v>
@@ -2792,25 +2792,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>101000</v>
+        <v>104400</v>
       </c>
       <c r="E72" s="3">
-        <v>130300</v>
+        <v>942800</v>
       </c>
       <c r="F72" s="3">
-        <v>175600</v>
+        <v>1271200</v>
       </c>
       <c r="G72" s="3">
-        <v>156600</v>
+        <v>1133400</v>
       </c>
       <c r="H72" s="3">
-        <v>125800</v>
+        <v>910600</v>
       </c>
       <c r="I72" s="3">
-        <v>47000</v>
+        <v>340000</v>
       </c>
       <c r="J72" s="3">
-        <v>18100</v>
+        <v>131200</v>
       </c>
       <c r="K72" s="3">
         <v>-5100</v>
@@ -2936,25 +2936,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>344400</v>
+        <v>350900</v>
       </c>
       <c r="E76" s="3">
-        <v>369200</v>
+        <v>2672500</v>
       </c>
       <c r="F76" s="3">
-        <v>403500</v>
+        <v>2920300</v>
       </c>
       <c r="G76" s="3">
-        <v>377200</v>
+        <v>2730300</v>
       </c>
       <c r="H76" s="3">
-        <v>345500</v>
+        <v>2500800</v>
       </c>
       <c r="I76" s="3">
-        <v>250200</v>
+        <v>1810900</v>
       </c>
       <c r="J76" s="3">
-        <v>31200</v>
+        <v>225800</v>
       </c>
       <c r="K76" s="3">
         <v>4200</v>
@@ -3049,25 +3049,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-29300</v>
+        <v>-212100</v>
       </c>
       <c r="E81" s="3">
-        <v>-39800</v>
+        <v>-288300</v>
       </c>
       <c r="F81" s="3">
-        <v>19000</v>
+        <v>137800</v>
       </c>
       <c r="G81" s="3">
-        <v>31600</v>
+        <v>228800</v>
       </c>
       <c r="H81" s="3">
-        <v>79100</v>
+        <v>572700</v>
       </c>
       <c r="I81" s="3">
-        <v>15700</v>
+        <v>113500</v>
       </c>
       <c r="J81" s="3">
-        <v>6400</v>
+        <v>46100</v>
       </c>
       <c r="K81" s="3">
         <v>-1700</v>
@@ -3101,25 +3101,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>7500</v>
+        <v>54500</v>
       </c>
       <c r="E83" s="3">
-        <v>8100</v>
+        <v>58600</v>
       </c>
       <c r="F83" s="3">
-        <v>7200</v>
+        <v>51900</v>
       </c>
       <c r="G83" s="3">
+        <v>27100</v>
+      </c>
+      <c r="H83" s="3">
+        <v>17200</v>
+      </c>
+      <c r="I83" s="3">
+        <v>6200</v>
+      </c>
+      <c r="J83" s="3">
         <v>3700</v>
-      </c>
-      <c r="H83" s="3">
-        <v>2400</v>
-      </c>
-      <c r="I83" s="3">
-        <v>900</v>
-      </c>
-      <c r="J83" s="3">
-        <v>500</v>
       </c>
       <c r="K83" s="3">
         <v>300</v>
@@ -3317,25 +3317,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>41300</v>
+        <v>298700</v>
       </c>
       <c r="E89" s="3">
-        <v>-108800</v>
+        <v>-787600</v>
       </c>
       <c r="F89" s="3">
-        <v>-32100</v>
+        <v>-232400</v>
       </c>
       <c r="G89" s="3">
-        <v>21700</v>
+        <v>157300</v>
       </c>
       <c r="H89" s="3">
-        <v>59100</v>
+        <v>428000</v>
       </c>
       <c r="I89" s="3">
-        <v>97800</v>
+        <v>707600</v>
       </c>
       <c r="J89" s="3">
-        <v>32900</v>
+        <v>238300</v>
       </c>
       <c r="K89" s="3">
         <v>2400</v>
@@ -3369,25 +3369,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-1600</v>
+        <v>-11300</v>
       </c>
       <c r="E91" s="3">
-        <v>-1100</v>
+        <v>-8100</v>
       </c>
       <c r="F91" s="3">
-        <v>-6400</v>
+        <v>-46100</v>
       </c>
       <c r="G91" s="3">
-        <v>-11500</v>
+        <v>-83600</v>
       </c>
       <c r="H91" s="3">
-        <v>-4700</v>
+        <v>-34300</v>
       </c>
       <c r="I91" s="3">
-        <v>-2400</v>
+        <v>-17100</v>
       </c>
       <c r="J91" s="3">
-        <v>-3000</v>
+        <v>-21500</v>
       </c>
       <c r="K91" s="3">
         <v>-1400</v>
@@ -3477,25 +3477,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>7600</v>
+        <v>54700</v>
       </c>
       <c r="E94" s="3">
-        <v>-5800</v>
+        <v>-42300</v>
       </c>
       <c r="F94" s="3">
-        <v>-147700</v>
+        <v>-1069300</v>
       </c>
       <c r="G94" s="3">
-        <v>-28600</v>
+        <v>-206900</v>
       </c>
       <c r="H94" s="3">
-        <v>-15600</v>
+        <v>-112700</v>
       </c>
       <c r="I94" s="3">
-        <v>-44900</v>
+        <v>-324800</v>
       </c>
       <c r="J94" s="3">
-        <v>-5400</v>
+        <v>-38900</v>
       </c>
       <c r="K94" s="3">
         <v>-13800</v>
@@ -3532,7 +3532,7 @@
         <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>-5500</v>
+        <v>-40000</v>
       </c>
       <c r="F96" s="3">
         <v>0</v>
@@ -3673,25 +3673,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-40800</v>
+        <v>-295000</v>
       </c>
       <c r="E100" s="3">
-        <v>40000</v>
+        <v>289200</v>
       </c>
       <c r="F100" s="3">
-        <v>76100</v>
+        <v>551100</v>
       </c>
       <c r="G100" s="3">
-        <v>78000</v>
+        <v>564700</v>
       </c>
       <c r="H100" s="3">
-        <v>3500</v>
+        <v>25600</v>
       </c>
       <c r="I100" s="3">
-        <v>88300</v>
+        <v>639200</v>
       </c>
       <c r="J100" s="3">
-        <v>2800</v>
+        <v>20100</v>
       </c>
       <c r="K100" s="3">
         <v>1400</v>
@@ -3709,25 +3709,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-4700</v>
+        <v>-34400</v>
       </c>
       <c r="E101" s="3">
-        <v>600</v>
+        <v>4500</v>
       </c>
       <c r="F101" s="3">
-        <v>-2200</v>
+        <v>-15600</v>
       </c>
       <c r="G101" s="3">
-        <v>-6000</v>
+        <v>-43300</v>
       </c>
       <c r="H101" s="3">
-        <v>1600</v>
+        <v>11300</v>
       </c>
       <c r="I101" s="3">
-        <v>8300</v>
+        <v>60400</v>
       </c>
       <c r="J101" s="3">
-        <v>-400</v>
+        <v>-3200</v>
       </c>
       <c r="K101" s="3">
         <v>700</v>
@@ -3745,25 +3745,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>3300</v>
+        <v>24000</v>
       </c>
       <c r="E102" s="3">
-        <v>-74100</v>
+        <v>-536200</v>
       </c>
       <c r="F102" s="3">
-        <v>-105900</v>
+        <v>-766200</v>
       </c>
       <c r="G102" s="3">
-        <v>65200</v>
+        <v>471800</v>
       </c>
       <c r="H102" s="3">
-        <v>48700</v>
+        <v>352200</v>
       </c>
       <c r="I102" s="3">
-        <v>149500</v>
+        <v>1082300</v>
       </c>
       <c r="J102" s="3">
-        <v>29900</v>
+        <v>216400</v>
       </c>
       <c r="K102" s="3">
         <v>-9300</v>

--- a/AAII_Financials/Yearly/ZEPP_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ZEPP_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="92">
   <si>
     <t>ZEPP</t>
   </si>
@@ -718,25 +718,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>2495300</v>
+        <v>351900</v>
       </c>
       <c r="E8" s="3">
-        <v>4142900</v>
+        <v>600700</v>
       </c>
       <c r="F8" s="3">
-        <v>6250100</v>
+        <v>983900</v>
       </c>
       <c r="G8" s="3">
-        <v>6433400</v>
+        <v>985400</v>
       </c>
       <c r="H8" s="3">
-        <v>5812300</v>
+        <v>834700</v>
       </c>
       <c r="I8" s="3">
-        <v>3645300</v>
+        <v>530000</v>
       </c>
       <c r="J8" s="3">
-        <v>2048900</v>
+        <v>314900</v>
       </c>
       <c r="K8" s="3">
         <v>216400</v>
@@ -754,25 +754,25 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>1837500</v>
+        <v>259100</v>
       </c>
       <c r="E9" s="3">
-        <v>3339700</v>
+        <v>484200</v>
       </c>
       <c r="F9" s="3">
-        <v>4944500</v>
+        <v>778300</v>
       </c>
       <c r="G9" s="3">
-        <v>5100700</v>
+        <v>781300</v>
       </c>
       <c r="H9" s="3">
-        <v>4344500</v>
+        <v>624000</v>
       </c>
       <c r="I9" s="3">
-        <v>2705900</v>
+        <v>393400</v>
       </c>
       <c r="J9" s="3">
-        <v>1554200</v>
+        <v>238900</v>
       </c>
       <c r="K9" s="3">
         <v>178000</v>
@@ -790,25 +790,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>657800</v>
+        <v>92800</v>
       </c>
       <c r="E10" s="3">
-        <v>803100</v>
+        <v>116400</v>
       </c>
       <c r="F10" s="3">
-        <v>1305600</v>
+        <v>205500</v>
       </c>
       <c r="G10" s="3">
-        <v>1332700</v>
+        <v>204100</v>
       </c>
       <c r="H10" s="3">
-        <v>1467700</v>
+        <v>210800</v>
       </c>
       <c r="I10" s="3">
-        <v>939500</v>
+        <v>136600</v>
       </c>
       <c r="J10" s="3">
-        <v>494700</v>
+        <v>76000</v>
       </c>
       <c r="K10" s="3">
         <v>38400</v>
@@ -842,25 +842,25 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>361800</v>
+        <v>51000</v>
       </c>
       <c r="E12" s="3">
-        <v>517100</v>
+        <v>75000</v>
       </c>
       <c r="F12" s="3">
-        <v>515100</v>
+        <v>81100</v>
       </c>
       <c r="G12" s="3">
-        <v>538000</v>
+        <v>82400</v>
       </c>
       <c r="H12" s="3">
-        <v>430800</v>
+        <v>61900</v>
       </c>
       <c r="I12" s="3">
-        <v>263200</v>
+        <v>38300</v>
       </c>
       <c r="J12" s="3">
-        <v>153800</v>
+        <v>23600</v>
       </c>
       <c r="K12" s="3">
         <v>18400</v>
@@ -914,25 +914,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>2300</v>
+        <v>0</v>
       </c>
       <c r="E14" s="3">
-        <v>13900</v>
+        <v>-5600</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>-2100</v>
       </c>
       <c r="G14" s="3">
-        <v>-56500</v>
+        <v>-10500</v>
       </c>
       <c r="H14" s="3">
-        <v>2600</v>
+        <v>100</v>
       </c>
       <c r="I14" s="3">
-        <v>7600</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="J14" s="3">
+        <v>-400</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
@@ -950,25 +950,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>7700</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>8500</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>8200</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>4200</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -999,25 +999,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2704700</v>
+        <v>381100</v>
       </c>
       <c r="E17" s="3">
-        <v>4567000</v>
+        <v>660100</v>
       </c>
       <c r="F17" s="3">
-        <v>6156200</v>
+        <v>969100</v>
       </c>
       <c r="G17" s="3">
-        <v>6202600</v>
+        <v>958700</v>
       </c>
       <c r="H17" s="3">
-        <v>5208400</v>
+        <v>747600</v>
       </c>
       <c r="I17" s="3">
-        <v>3287200</v>
+        <v>476800</v>
       </c>
       <c r="J17" s="3">
-        <v>1866900</v>
+        <v>286900</v>
       </c>
       <c r="K17" s="3">
         <v>214500</v>
@@ -1035,25 +1035,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-209400</v>
+        <v>-29200</v>
       </c>
       <c r="E18" s="3">
-        <v>-424100</v>
+        <v>-59500</v>
       </c>
       <c r="F18" s="3">
-        <v>93900</v>
+        <v>14800</v>
       </c>
       <c r="G18" s="3">
-        <v>230700</v>
+        <v>26700</v>
       </c>
       <c r="H18" s="3">
-        <v>603900</v>
+        <v>87100</v>
       </c>
       <c r="I18" s="3">
-        <v>358100</v>
+        <v>53200</v>
       </c>
       <c r="J18" s="3">
-        <v>182000</v>
+        <v>28000</v>
       </c>
       <c r="K18" s="3">
         <v>1900</v>
@@ -1087,25 +1087,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>20300</v>
+        <v>-700</v>
       </c>
       <c r="E20" s="3">
-        <v>108600</v>
+        <v>-8900</v>
       </c>
       <c r="F20" s="3">
-        <v>57600</v>
+        <v>-10800</v>
       </c>
       <c r="G20" s="3">
-        <v>34900</v>
+        <v>900</v>
       </c>
       <c r="H20" s="3">
-        <v>48500</v>
+        <v>-1700</v>
       </c>
       <c r="I20" s="3">
-        <v>28500</v>
+        <v>-1500</v>
       </c>
       <c r="J20" s="3">
-        <v>9900</v>
+        <v>-1100</v>
       </c>
       <c r="K20" s="3">
         <v>2200</v>
@@ -1123,25 +1123,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-134600</v>
+        <v>-20900</v>
       </c>
       <c r="E21" s="3">
-        <v>-256900</v>
+        <v>-42100</v>
       </c>
       <c r="F21" s="3">
-        <v>203400</v>
+        <v>33700</v>
       </c>
       <c r="G21" s="3">
-        <v>292700</v>
+        <v>30000</v>
       </c>
       <c r="H21" s="3">
-        <v>669600</v>
+        <v>91300</v>
       </c>
       <c r="I21" s="3">
-        <v>392800</v>
+        <v>55600</v>
       </c>
       <c r="J21" s="3">
-        <v>195600</v>
+        <v>29700</v>
       </c>
       <c r="K21" s="3">
         <v>4300</v>
@@ -1159,16 +1159,16 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>47700</v>
+        <v>6700</v>
       </c>
       <c r="E22" s="3">
-        <v>57000</v>
+        <v>8300</v>
       </c>
       <c r="F22" s="3">
-        <v>44900</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
+        <v>7100</v>
+      </c>
+      <c r="G22" s="3">
+        <v>3500</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>3</v>
@@ -1195,25 +1195,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-236800</v>
+        <v>-32200</v>
       </c>
       <c r="E23" s="3">
-        <v>-372500</v>
+        <v>-51500</v>
       </c>
       <c r="F23" s="3">
-        <v>106700</v>
+        <v>23200</v>
       </c>
       <c r="G23" s="3">
-        <v>265600</v>
+        <v>40000</v>
       </c>
       <c r="H23" s="3">
-        <v>652400</v>
+        <v>93500</v>
       </c>
       <c r="I23" s="3">
-        <v>386600</v>
+        <v>56500</v>
       </c>
       <c r="J23" s="3">
-        <v>191900</v>
+        <v>29900</v>
       </c>
       <c r="K23" s="3">
         <v>4000</v>
@@ -1231,25 +1231,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-15800</v>
+        <v>-2200</v>
       </c>
       <c r="E24" s="3">
-        <v>-65900</v>
+        <v>-9600</v>
       </c>
       <c r="F24" s="3">
-        <v>10700</v>
+        <v>1700</v>
       </c>
       <c r="G24" s="3">
-        <v>31200</v>
+        <v>4800</v>
       </c>
       <c r="H24" s="3">
-        <v>77900</v>
+        <v>11200</v>
       </c>
       <c r="I24" s="3">
-        <v>52000</v>
+        <v>7600</v>
       </c>
       <c r="J24" s="3">
-        <v>23400</v>
+        <v>4200</v>
       </c>
       <c r="K24" s="3">
         <v>400</v>
@@ -1303,25 +1303,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-221000</v>
+        <v>-30000</v>
       </c>
       <c r="E26" s="3">
-        <v>-306700</v>
+        <v>-41900</v>
       </c>
       <c r="F26" s="3">
-        <v>95900</v>
+        <v>21600</v>
       </c>
       <c r="G26" s="3">
-        <v>234500</v>
+        <v>35200</v>
       </c>
       <c r="H26" s="3">
-        <v>574500</v>
+        <v>82300</v>
       </c>
       <c r="I26" s="3">
-        <v>334600</v>
+        <v>48900</v>
       </c>
       <c r="J26" s="3">
-        <v>168500</v>
+        <v>25700</v>
       </c>
       <c r="K26" s="3">
         <v>3600</v>
@@ -1339,25 +1339,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-212100</v>
+        <v>-29900</v>
       </c>
       <c r="E27" s="3">
-        <v>-288300</v>
+        <v>-41800</v>
       </c>
       <c r="F27" s="3">
-        <v>137800</v>
+        <v>21700</v>
       </c>
       <c r="G27" s="3">
-        <v>228800</v>
+        <v>35000</v>
       </c>
       <c r="H27" s="3">
-        <v>572700</v>
+        <v>82300</v>
       </c>
       <c r="I27" s="3">
-        <v>113500</v>
+        <v>16500</v>
       </c>
       <c r="J27" s="3">
-        <v>50300</v>
+        <v>7100</v>
       </c>
       <c r="K27" s="3">
         <v>-1700</v>
@@ -1410,26 +1410,26 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>3</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>-4200</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>3</v>
@@ -1519,25 +1519,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-20300</v>
+        <v>700</v>
       </c>
       <c r="E32" s="3">
-        <v>-108600</v>
+        <v>8900</v>
       </c>
       <c r="F32" s="3">
-        <v>-57600</v>
+        <v>10800</v>
       </c>
       <c r="G32" s="3">
-        <v>-34900</v>
+        <v>-900</v>
       </c>
       <c r="H32" s="3">
-        <v>-48500</v>
+        <v>1700</v>
       </c>
       <c r="I32" s="3">
-        <v>-28500</v>
+        <v>1500</v>
       </c>
       <c r="J32" s="3">
-        <v>-9900</v>
+        <v>1100</v>
       </c>
       <c r="K32" s="3">
         <v>-2200</v>
@@ -1555,25 +1555,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-212100</v>
+        <v>-29900</v>
       </c>
       <c r="E33" s="3">
-        <v>-288300</v>
+        <v>-41800</v>
       </c>
       <c r="F33" s="3">
-        <v>137800</v>
+        <v>21700</v>
       </c>
       <c r="G33" s="3">
-        <v>228800</v>
+        <v>35000</v>
       </c>
       <c r="H33" s="3">
-        <v>572700</v>
+        <v>82600</v>
       </c>
       <c r="I33" s="3">
-        <v>113500</v>
+        <v>49400</v>
       </c>
       <c r="J33" s="3">
-        <v>46100</v>
+        <v>25800</v>
       </c>
       <c r="K33" s="3">
         <v>-1700</v>
@@ -1627,25 +1627,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-212100</v>
+        <v>-29900</v>
       </c>
       <c r="E35" s="3">
-        <v>-288300</v>
+        <v>-41800</v>
       </c>
       <c r="F35" s="3">
-        <v>137800</v>
+        <v>21700</v>
       </c>
       <c r="G35" s="3">
-        <v>228800</v>
+        <v>35000</v>
       </c>
       <c r="H35" s="3">
-        <v>572700</v>
+        <v>82600</v>
       </c>
       <c r="I35" s="3">
-        <v>113500</v>
+        <v>49400</v>
       </c>
       <c r="J35" s="3">
-        <v>46100</v>
+        <v>25800</v>
       </c>
       <c r="K35" s="3">
         <v>-1700</v>
@@ -1736,25 +1736,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>133700</v>
+        <v>133800</v>
       </c>
       <c r="E41" s="3">
-        <v>886600</v>
+        <v>128500</v>
       </c>
       <c r="F41" s="3">
-        <v>1473500</v>
+        <v>231200</v>
       </c>
       <c r="G41" s="3">
-        <v>2278300</v>
+        <v>348200</v>
       </c>
       <c r="H41" s="3">
-        <v>1803100</v>
+        <v>259000</v>
       </c>
       <c r="I41" s="3">
-        <v>1538800</v>
+        <v>209600</v>
       </c>
       <c r="J41" s="3">
-        <v>366300</v>
+        <v>56300</v>
       </c>
       <c r="K41" s="3">
         <v>21300</v>
@@ -1775,22 +1775,22 @@
         <v>5200</v>
       </c>
       <c r="E42" s="3">
-        <v>34300</v>
+        <v>5000</v>
       </c>
       <c r="F42" s="3">
-        <v>19400</v>
+        <v>3800</v>
       </c>
       <c r="G42" s="3">
-        <v>18400</v>
+        <v>3600</v>
       </c>
       <c r="H42" s="3">
-        <v>17200</v>
+        <v>2500</v>
       </c>
       <c r="I42" s="3">
-        <v>50500</v>
+        <v>21400</v>
       </c>
       <c r="J42" s="3">
-        <v>13700</v>
+        <v>2100</v>
       </c>
       <c r="K42" s="3">
         <v>1300</v>
@@ -1808,25 +1808,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>590200</v>
+        <v>82100</v>
       </c>
       <c r="E43" s="3">
-        <v>870300</v>
+        <v>126200</v>
       </c>
       <c r="F43" s="3">
-        <v>1087900</v>
+        <v>171300</v>
       </c>
       <c r="G43" s="3">
-        <v>1280000</v>
+        <v>196100</v>
       </c>
       <c r="H43" s="3">
-        <v>1664000</v>
+        <v>232700</v>
       </c>
       <c r="I43" s="3">
-        <v>757500</v>
+        <v>107300</v>
       </c>
       <c r="J43" s="3">
-        <v>641000</v>
+        <v>96500</v>
       </c>
       <c r="K43" s="3">
         <v>69300</v>
@@ -1844,25 +1844,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>687600</v>
+        <v>85000</v>
       </c>
       <c r="E44" s="3">
-        <v>1021900</v>
+        <v>148200</v>
       </c>
       <c r="F44" s="3">
-        <v>1249300</v>
+        <v>196700</v>
       </c>
       <c r="G44" s="3">
-        <v>1217500</v>
+        <v>186500</v>
       </c>
       <c r="H44" s="3">
-        <v>893800</v>
+        <v>128400</v>
       </c>
       <c r="I44" s="3">
-        <v>484600</v>
+        <v>70500</v>
       </c>
       <c r="J44" s="3">
-        <v>249700</v>
+        <v>38400</v>
       </c>
       <c r="K44" s="3">
         <v>26700</v>
@@ -1880,25 +1880,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>53900</v>
+        <v>200</v>
       </c>
       <c r="E45" s="3">
-        <v>145400</v>
+        <v>700</v>
       </c>
       <c r="F45" s="3">
-        <v>100800</v>
+        <v>1400</v>
       </c>
       <c r="G45" s="3">
-        <v>33600</v>
+        <v>800</v>
       </c>
       <c r="H45" s="3">
-        <v>14400</v>
+        <v>6800</v>
       </c>
       <c r="I45" s="3">
-        <v>26100</v>
+        <v>4700</v>
       </c>
       <c r="J45" s="3">
-        <v>24600</v>
+        <v>5200</v>
       </c>
       <c r="K45" s="3">
         <v>900</v>
@@ -1916,25 +1916,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>316700</v>
+        <v>317100</v>
       </c>
       <c r="E46" s="3">
-        <v>2958500</v>
+        <v>428900</v>
       </c>
       <c r="F46" s="3">
-        <v>3931000</v>
+        <v>618800</v>
       </c>
       <c r="G46" s="3">
-        <v>4827900</v>
+        <v>739500</v>
       </c>
       <c r="H46" s="3">
-        <v>4392500</v>
+        <v>630800</v>
       </c>
       <c r="I46" s="3">
-        <v>2857500</v>
+        <v>415500</v>
       </c>
       <c r="J46" s="3">
-        <v>1295400</v>
+        <v>199100</v>
       </c>
       <c r="K46" s="3">
         <v>119500</v>
@@ -1952,25 +1952,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1935100</v>
+        <v>238800</v>
       </c>
       <c r="E47" s="3">
-        <v>1693000</v>
+        <v>244500</v>
       </c>
       <c r="F47" s="3">
-        <v>1552600</v>
+        <v>244400</v>
       </c>
       <c r="G47" s="3">
-        <v>444000</v>
+        <v>68000</v>
       </c>
       <c r="H47" s="3">
-        <v>406100</v>
+        <v>58300</v>
       </c>
       <c r="I47" s="3">
-        <v>208900</v>
+        <v>30400</v>
       </c>
       <c r="J47" s="3">
-        <v>85200</v>
+        <v>13100</v>
       </c>
       <c r="K47" s="3">
         <v>10900</v>
@@ -1988,25 +1988,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>127600</v>
+        <v>15800</v>
       </c>
       <c r="E48" s="3">
-        <v>166200</v>
+        <v>24100</v>
       </c>
       <c r="F48" s="3">
-        <v>242300</v>
+        <v>38100</v>
       </c>
       <c r="G48" s="3">
-        <v>275800</v>
+        <v>42200</v>
       </c>
       <c r="H48" s="3">
-        <v>173000</v>
+        <v>24900</v>
       </c>
       <c r="I48" s="3">
-        <v>40000</v>
+        <v>5800</v>
       </c>
       <c r="J48" s="3">
-        <v>28800</v>
+        <v>4400</v>
       </c>
       <c r="K48" s="3">
         <v>1500</v>
@@ -2024,25 +2024,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>89500</v>
+        <v>19500</v>
       </c>
       <c r="E49" s="3">
-        <v>189400</v>
+        <v>27500</v>
       </c>
       <c r="F49" s="3">
-        <v>196600</v>
+        <v>31000</v>
       </c>
       <c r="G49" s="3">
-        <v>207700</v>
+        <v>31800</v>
       </c>
       <c r="H49" s="3">
-        <v>91700</v>
+        <v>13200</v>
       </c>
       <c r="I49" s="3">
-        <v>69700</v>
+        <v>10100</v>
       </c>
       <c r="J49" s="3">
-        <v>11300</v>
+        <v>1700</v>
       </c>
       <c r="K49" s="3">
         <v>200</v>
@@ -2132,25 +2132,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>42100</v>
+        <v>9700</v>
       </c>
       <c r="E52" s="3">
-        <v>260600</v>
+        <v>7300</v>
       </c>
       <c r="F52" s="3">
-        <v>163000</v>
+        <v>3100</v>
       </c>
       <c r="G52" s="3">
-        <v>148400</v>
+        <v>4300</v>
       </c>
       <c r="H52" s="3">
-        <v>111500</v>
+        <v>1300</v>
       </c>
       <c r="I52" s="3">
-        <v>82400</v>
+        <v>1100</v>
       </c>
       <c r="J52" s="3">
-        <v>44900</v>
+        <v>500</v>
       </c>
       <c r="K52" s="3">
         <v>3200</v>
@@ -2204,25 +2204,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>635500</v>
+        <v>636300</v>
       </c>
       <c r="E54" s="3">
-        <v>5267600</v>
+        <v>763700</v>
       </c>
       <c r="F54" s="3">
-        <v>6085500</v>
+        <v>958000</v>
       </c>
       <c r="G54" s="3">
-        <v>5903700</v>
+        <v>904300</v>
       </c>
       <c r="H54" s="3">
-        <v>5174700</v>
+        <v>743200</v>
       </c>
       <c r="I54" s="3">
-        <v>3258500</v>
+        <v>473800</v>
       </c>
       <c r="J54" s="3">
-        <v>1465500</v>
+        <v>225200</v>
       </c>
       <c r="K54" s="3">
         <v>135300</v>
@@ -2272,25 +2272,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>40800</v>
+        <v>106300</v>
       </c>
       <c r="E57" s="3">
-        <v>497600</v>
+        <v>138000</v>
       </c>
       <c r="F57" s="3">
-        <v>1367400</v>
+        <v>231300</v>
       </c>
       <c r="G57" s="3">
-        <v>1962500</v>
+        <v>298900</v>
       </c>
       <c r="H57" s="3">
-        <v>2014700</v>
+        <v>287500</v>
       </c>
       <c r="I57" s="3">
-        <v>1074800</v>
+        <v>157500</v>
       </c>
       <c r="J57" s="3">
-        <v>715900</v>
+        <v>109600</v>
       </c>
       <c r="K57" s="3">
         <v>76100</v>
@@ -2308,25 +2308,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>68700</v>
+        <v>5600</v>
       </c>
       <c r="E58" s="3">
-        <v>968400</v>
+        <v>80400</v>
       </c>
       <c r="F58" s="3">
-        <v>461800</v>
+        <v>64200</v>
       </c>
       <c r="G58" s="3">
-        <v>504700</v>
+        <v>84700</v>
       </c>
       <c r="H58" s="3">
-        <v>2200</v>
+        <v>4700</v>
       </c>
       <c r="I58" s="3">
-        <v>38900</v>
+        <v>2900</v>
       </c>
       <c r="J58" s="3">
-        <v>35200</v>
+        <v>4600</v>
       </c>
       <c r="K58" s="3">
         <v>1800</v>
@@ -2344,25 +2344,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>361300</v>
+        <v>35400</v>
       </c>
       <c r="E59" s="3">
-        <v>202700</v>
+        <v>14800</v>
       </c>
       <c r="F59" s="3">
-        <v>322900</v>
+        <v>29100</v>
       </c>
       <c r="G59" s="3">
-        <v>322500</v>
+        <v>32800</v>
       </c>
       <c r="H59" s="3">
-        <v>464900</v>
+        <v>42300</v>
       </c>
       <c r="I59" s="3">
-        <v>274000</v>
+        <v>25500</v>
       </c>
       <c r="J59" s="3">
-        <v>126100</v>
+        <v>11600</v>
       </c>
       <c r="K59" s="3">
         <v>10300</v>
@@ -2380,25 +2380,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>155100</v>
+        <v>155300</v>
       </c>
       <c r="E60" s="3">
-        <v>1668700</v>
+        <v>241900</v>
       </c>
       <c r="F60" s="3">
-        <v>2152100</v>
+        <v>338800</v>
       </c>
       <c r="G60" s="3">
-        <v>2789700</v>
+        <v>427300</v>
       </c>
       <c r="H60" s="3">
-        <v>2481800</v>
+        <v>356400</v>
       </c>
       <c r="I60" s="3">
-        <v>1387700</v>
+        <v>201800</v>
       </c>
       <c r="J60" s="3">
-        <v>877200</v>
+        <v>134800</v>
       </c>
       <c r="K60" s="3">
         <v>88200</v>
@@ -2416,19 +2416,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>120000</v>
+        <v>123400</v>
       </c>
       <c r="E61" s="3">
-        <v>684200</v>
+        <v>103800</v>
       </c>
       <c r="F61" s="3">
-        <v>726900</v>
+        <v>125600</v>
       </c>
       <c r="G61" s="3">
-        <v>60000</v>
+        <v>27000</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
@@ -2451,26 +2451,26 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>7600</v>
-      </c>
-      <c r="E62" s="3">
-        <v>229800</v>
-      </c>
-      <c r="F62" s="3">
-        <v>273100</v>
-      </c>
-      <c r="G62" s="3">
-        <v>323800</v>
-      </c>
-      <c r="H62" s="3">
-        <v>195400</v>
-      </c>
-      <c r="I62" s="3">
-        <v>61200</v>
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J62" s="3">
-        <v>10500</v>
+        <v>1200</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -2596,25 +2596,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>284600</v>
+        <v>283100</v>
       </c>
       <c r="E66" s="3">
-        <v>2595100</v>
+        <v>374500</v>
       </c>
       <c r="F66" s="3">
-        <v>3165200</v>
+        <v>496200</v>
       </c>
       <c r="G66" s="3">
-        <v>3173500</v>
+        <v>486100</v>
       </c>
       <c r="H66" s="3">
-        <v>2674000</v>
+        <v>384500</v>
       </c>
       <c r="I66" s="3">
-        <v>1447600</v>
+        <v>210700</v>
       </c>
       <c r="J66" s="3">
-        <v>890100</v>
+        <v>136400</v>
       </c>
       <c r="K66" s="3">
         <v>88200</v>
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="J70" s="3">
-        <v>349600</v>
+        <v>53700</v>
       </c>
       <c r="K70" s="3">
         <v>42900</v>
@@ -2792,25 +2792,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>104400</v>
+        <v>103100</v>
       </c>
       <c r="E72" s="3">
-        <v>942800</v>
+        <v>136700</v>
       </c>
       <c r="F72" s="3">
-        <v>1271200</v>
+        <v>200100</v>
       </c>
       <c r="G72" s="3">
-        <v>1133400</v>
+        <v>173600</v>
       </c>
       <c r="H72" s="3">
-        <v>910600</v>
+        <v>130800</v>
       </c>
       <c r="I72" s="3">
-        <v>340000</v>
+        <v>49400</v>
       </c>
       <c r="J72" s="3">
-        <v>131200</v>
+        <v>20200</v>
       </c>
       <c r="K72" s="3">
         <v>-5100</v>
@@ -2936,25 +2936,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>350900</v>
+        <v>351500</v>
       </c>
       <c r="E76" s="3">
-        <v>2672500</v>
+        <v>387500</v>
       </c>
       <c r="F76" s="3">
-        <v>2920300</v>
+        <v>459700</v>
       </c>
       <c r="G76" s="3">
-        <v>2730300</v>
+        <v>418200</v>
       </c>
       <c r="H76" s="3">
-        <v>2500800</v>
+        <v>359200</v>
       </c>
       <c r="I76" s="3">
-        <v>1810900</v>
+        <v>263300</v>
       </c>
       <c r="J76" s="3">
-        <v>225800</v>
+        <v>34700</v>
       </c>
       <c r="K76" s="3">
         <v>4200</v>
@@ -3049,25 +3049,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-212100</v>
+        <v>-29900</v>
       </c>
       <c r="E81" s="3">
-        <v>-288300</v>
+        <v>-41800</v>
       </c>
       <c r="F81" s="3">
-        <v>137800</v>
+        <v>21700</v>
       </c>
       <c r="G81" s="3">
-        <v>228800</v>
+        <v>35000</v>
       </c>
       <c r="H81" s="3">
-        <v>572700</v>
+        <v>82600</v>
       </c>
       <c r="I81" s="3">
-        <v>113500</v>
+        <v>49400</v>
       </c>
       <c r="J81" s="3">
-        <v>46100</v>
+        <v>25800</v>
       </c>
       <c r="K81" s="3">
         <v>-1700</v>
@@ -3101,25 +3101,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>54500</v>
+        <v>5200</v>
       </c>
       <c r="E83" s="3">
-        <v>58600</v>
+        <v>6000</v>
       </c>
       <c r="F83" s="3">
-        <v>51900</v>
+        <v>5500</v>
       </c>
       <c r="G83" s="3">
-        <v>27100</v>
+        <v>2300</v>
       </c>
       <c r="H83" s="3">
-        <v>17200</v>
+        <v>1400</v>
       </c>
       <c r="I83" s="3">
-        <v>6200</v>
+        <v>800</v>
       </c>
       <c r="J83" s="3">
-        <v>3700</v>
+        <v>500</v>
       </c>
       <c r="K83" s="3">
         <v>300</v>
@@ -3317,25 +3317,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>298700</v>
+        <v>42100</v>
       </c>
       <c r="E89" s="3">
-        <v>-787600</v>
+        <v>-114200</v>
       </c>
       <c r="F89" s="3">
-        <v>-232400</v>
+        <v>-36600</v>
       </c>
       <c r="G89" s="3">
-        <v>157300</v>
+        <v>24100</v>
       </c>
       <c r="H89" s="3">
-        <v>428000</v>
+        <v>61500</v>
       </c>
       <c r="I89" s="3">
-        <v>707600</v>
+        <v>102900</v>
       </c>
       <c r="J89" s="3">
-        <v>238300</v>
+        <v>36600</v>
       </c>
       <c r="K89" s="3">
         <v>2400</v>
@@ -3369,25 +3369,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-11300</v>
+        <v>-1600</v>
       </c>
       <c r="E91" s="3">
-        <v>-8100</v>
+        <v>-1200</v>
       </c>
       <c r="F91" s="3">
-        <v>-46100</v>
+        <v>-7200</v>
       </c>
       <c r="G91" s="3">
-        <v>-83600</v>
+        <v>-12800</v>
       </c>
       <c r="H91" s="3">
-        <v>-34300</v>
+        <v>-4900</v>
       </c>
       <c r="I91" s="3">
-        <v>-17100</v>
+        <v>-2500</v>
       </c>
       <c r="J91" s="3">
-        <v>-21500</v>
+        <v>-3300</v>
       </c>
       <c r="K91" s="3">
         <v>-1400</v>
@@ -3477,25 +3477,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>54700</v>
+        <v>7700</v>
       </c>
       <c r="E94" s="3">
-        <v>-42300</v>
+        <v>-6100</v>
       </c>
       <c r="F94" s="3">
-        <v>-1069300</v>
+        <v>-168300</v>
       </c>
       <c r="G94" s="3">
-        <v>-206900</v>
+        <v>-31700</v>
       </c>
       <c r="H94" s="3">
-        <v>-112700</v>
+        <v>-16200</v>
       </c>
       <c r="I94" s="3">
-        <v>-324800</v>
+        <v>-47200</v>
       </c>
       <c r="J94" s="3">
-        <v>-38900</v>
+        <v>-6000</v>
       </c>
       <c r="K94" s="3">
         <v>-13800</v>
@@ -3532,7 +3532,7 @@
         <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>-40000</v>
+        <v>5800</v>
       </c>
       <c r="F96" s="3">
         <v>0</v>
@@ -3673,25 +3673,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-295000</v>
+        <v>-41600</v>
       </c>
       <c r="E100" s="3">
-        <v>289200</v>
+        <v>41900</v>
       </c>
       <c r="F100" s="3">
-        <v>551100</v>
+        <v>86700</v>
       </c>
       <c r="G100" s="3">
-        <v>564700</v>
+        <v>86500</v>
       </c>
       <c r="H100" s="3">
-        <v>25600</v>
+        <v>3700</v>
       </c>
       <c r="I100" s="3">
-        <v>639200</v>
+        <v>92900</v>
       </c>
       <c r="J100" s="3">
-        <v>20100</v>
+        <v>3100</v>
       </c>
       <c r="K100" s="3">
         <v>1400</v>
@@ -3709,25 +3709,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-34400</v>
+        <v>-4800</v>
       </c>
       <c r="E101" s="3">
-        <v>4500</v>
+        <v>700</v>
       </c>
       <c r="F101" s="3">
-        <v>-15600</v>
+        <v>-2500</v>
       </c>
       <c r="G101" s="3">
-        <v>-43300</v>
+        <v>-6600</v>
       </c>
       <c r="H101" s="3">
-        <v>11300</v>
+        <v>1600</v>
       </c>
       <c r="I101" s="3">
-        <v>60400</v>
+        <v>8800</v>
       </c>
       <c r="J101" s="3">
-        <v>-3200</v>
+        <v>-500</v>
       </c>
       <c r="K101" s="3">
         <v>700</v>
@@ -3745,25 +3745,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>24000</v>
+        <v>3400</v>
       </c>
       <c r="E102" s="3">
-        <v>-536200</v>
+        <v>-77700</v>
       </c>
       <c r="F102" s="3">
-        <v>-766200</v>
+        <v>-120600</v>
       </c>
       <c r="G102" s="3">
-        <v>471800</v>
+        <v>72300</v>
       </c>
       <c r="H102" s="3">
-        <v>352200</v>
+        <v>50600</v>
       </c>
       <c r="I102" s="3">
-        <v>1082300</v>
+        <v>157400</v>
       </c>
       <c r="J102" s="3">
-        <v>216400</v>
+        <v>33300</v>
       </c>
       <c r="K102" s="3">
         <v>-9300</v>

--- a/AAII_Financials/Yearly/ZEPP_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ZEPP_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="92">
   <si>
     <t>ZEPP</t>
   </si>
@@ -656,172 +656,184 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>351900</v>
+        <v>182600</v>
       </c>
       <c r="E8" s="3">
-        <v>600700</v>
+        <v>352900</v>
       </c>
       <c r="F8" s="3">
+        <v>613600</v>
+      </c>
+      <c r="G8" s="3">
         <v>983900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>985400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>834700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>530000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>314900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>216400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>128700</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>259100</v>
+        <v>112400</v>
       </c>
       <c r="E9" s="3">
-        <v>484200</v>
+        <v>260500</v>
       </c>
       <c r="F9" s="3">
+        <v>494800</v>
+      </c>
+      <c r="G9" s="3">
         <v>778300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>781300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>624000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>393400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>238900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>178000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>112900</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>92800</v>
+        <v>70200</v>
       </c>
       <c r="E10" s="3">
-        <v>116400</v>
+        <v>92400</v>
       </c>
       <c r="F10" s="3">
+        <v>118900</v>
+      </c>
+      <c r="G10" s="3">
         <v>205500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>204100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>210800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>136600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>76000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>38400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>15900</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -836,44 +848,48 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>51000</v>
+        <v>46200</v>
       </c>
       <c r="E12" s="3">
-        <v>75000</v>
+        <v>51500</v>
       </c>
       <c r="F12" s="3">
+        <v>77300</v>
+      </c>
+      <c r="G12" s="3">
         <v>81100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>82400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>61900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>38300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>23600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>18400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>8800</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O12" s="3"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -907,81 +923,90 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>8100</v>
       </c>
       <c r="E14" s="3">
-        <v>-5600</v>
+        <v>0</v>
       </c>
       <c r="F14" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="G14" s="3">
         <v>-2100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-10500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-400</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E15" s="3">
         <v>7700</v>
       </c>
-      <c r="E15" s="3">
-        <v>8500</v>
-      </c>
       <c r="F15" s="3">
+        <v>8700</v>
+      </c>
+      <c r="G15" s="3">
         <v>8200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>4200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>600</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -993,80 +1018,87 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>381100</v>
+        <v>229900</v>
       </c>
       <c r="E17" s="3">
-        <v>660100</v>
+        <v>383300</v>
       </c>
       <c r="F17" s="3">
+        <v>675500</v>
+      </c>
+      <c r="G17" s="3">
         <v>969100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>958700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>747600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>476800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>286900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>214500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>134500</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-29200</v>
+        <v>-47300</v>
       </c>
       <c r="E18" s="3">
-        <v>-59500</v>
+        <v>-30500</v>
       </c>
       <c r="F18" s="3">
+        <v>-61900</v>
+      </c>
+      <c r="G18" s="3">
         <v>14800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>26700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>87100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>53200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>28000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-5800</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N18" s="3"/>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O18" s="3"/>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1081,98 +1113,105 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-700</v>
+        <v>4900</v>
       </c>
       <c r="E20" s="3">
-        <v>-8900</v>
+        <v>-600</v>
       </c>
       <c r="F20" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="G20" s="3">
         <v>-10800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O20" s="3"/>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-20900</v>
+        <v>-47100</v>
       </c>
       <c r="E21" s="3">
-        <v>-42100</v>
+        <v>-22200</v>
       </c>
       <c r="F21" s="3">
+        <v>-44000</v>
+      </c>
+      <c r="G21" s="3">
         <v>33700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>30000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>91300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>55600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>29700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-5500</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N21" s="3"/>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3"/>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>6700</v>
+        <v>5600</v>
       </c>
       <c r="E22" s="3">
-        <v>8300</v>
+        <v>6800</v>
       </c>
       <c r="F22" s="3">
+        <v>8400</v>
+      </c>
+      <c r="G22" s="3">
         <v>7100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>3500</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1185,84 +1224,93 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
-      <c r="N22" s="3"/>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3"/>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-32200</v>
+        <v>-62100</v>
       </c>
       <c r="E23" s="3">
-        <v>-51500</v>
+        <v>-33500</v>
       </c>
       <c r="F23" s="3">
+        <v>-53200</v>
+      </c>
+      <c r="G23" s="3">
         <v>23200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>40000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>93500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>56500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>29900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-5600</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N23" s="3"/>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O23" s="3"/>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-2200</v>
+        <v>13700</v>
       </c>
       <c r="E24" s="3">
-        <v>-9600</v>
+        <v>-2400</v>
       </c>
       <c r="F24" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="G24" s="3">
         <v>1700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>4800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>11200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>7600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-100</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N24" s="3"/>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1296,81 +1344,90 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-      <c r="N25" s="3"/>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3"/>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-30000</v>
+        <v>-75800</v>
       </c>
       <c r="E26" s="3">
-        <v>-41900</v>
+        <v>-31100</v>
       </c>
       <c r="F26" s="3">
+        <v>-43300</v>
+      </c>
+      <c r="G26" s="3">
         <v>21600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>35200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>82300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>48900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>25700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-5400</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N26" s="3"/>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O26" s="3"/>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-29900</v>
+        <v>-75700</v>
       </c>
       <c r="E27" s="3">
-        <v>-41800</v>
+        <v>-31000</v>
       </c>
       <c r="F27" s="3">
+        <v>-43200</v>
+      </c>
+      <c r="G27" s="3">
         <v>21700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>35000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>82300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>16500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>7100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-8800</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N27" s="3"/>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O27" s="3"/>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1404,9 +1461,12 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-      <c r="N28" s="3"/>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3"/>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1431,8 +1491,8 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>3</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>3</v>
@@ -1440,9 +1500,12 @@
       <c r="M29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N29" s="3"/>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O29" s="3"/>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1476,9 +1539,12 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-      <c r="N30" s="3"/>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3"/>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1512,81 +1578,90 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-      <c r="N31" s="3"/>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3"/>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>700</v>
+        <v>-4900</v>
       </c>
       <c r="E32" s="3">
-        <v>8900</v>
+        <v>600</v>
       </c>
       <c r="F32" s="3">
+        <v>9100</v>
+      </c>
+      <c r="G32" s="3">
         <v>10800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N32" s="3"/>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O32" s="3"/>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-29900</v>
+        <v>-75700</v>
       </c>
       <c r="E33" s="3">
-        <v>-41800</v>
+        <v>-31000</v>
       </c>
       <c r="F33" s="3">
+        <v>-43200</v>
+      </c>
+      <c r="G33" s="3">
         <v>21700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>35000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>82600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>49400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>25800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-8800</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N33" s="3"/>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O33" s="3"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1620,86 +1695,95 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-      <c r="N34" s="3"/>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-29900</v>
+        <v>-75700</v>
       </c>
       <c r="E35" s="3">
-        <v>-41800</v>
+        <v>-31000</v>
       </c>
       <c r="F35" s="3">
+        <v>-43200</v>
+      </c>
+      <c r="G35" s="3">
         <v>21700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>35000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>82600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>49400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>25800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-8800</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N35" s="3"/>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O35" s="3"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N38" s="2"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O38" s="2"/>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1714,8 +1798,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1730,152 +1815,165 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>133800</v>
+        <v>91100</v>
       </c>
       <c r="E41" s="3">
+        <v>133700</v>
+      </c>
+      <c r="F41" s="3">
         <v>128500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>231200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>348200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>259000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>209600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>56300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>21300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>31600</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N41" s="3"/>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O41" s="3"/>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E42" s="3">
         <v>5200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>5000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>3800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>21400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1300</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N42" s="3"/>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O42" s="3"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>82100</v>
+        <v>79100</v>
       </c>
       <c r="E43" s="3">
+        <v>82000</v>
+      </c>
+      <c r="F43" s="3">
         <v>126200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>171300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>196100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>232700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>107300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>96500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>69300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>29500</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N43" s="3"/>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O43" s="3"/>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>85000</v>
+        <v>56800</v>
       </c>
       <c r="E44" s="3">
+        <v>84900</v>
+      </c>
+      <c r="F44" s="3">
         <v>148200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>196700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>186500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>128400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>70500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>38400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>26700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>12900</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N44" s="3"/>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O44" s="3"/>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -1883,179 +1981,194 @@
         <v>200</v>
       </c>
       <c r="E45" s="3">
+        <v>200</v>
+      </c>
+      <c r="F45" s="3">
         <v>700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>6800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>600</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N45" s="3"/>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O45" s="3"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>317100</v>
+        <v>251600</v>
       </c>
       <c r="E46" s="3">
+        <v>316700</v>
+      </c>
+      <c r="F46" s="3">
         <v>428900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>618800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>739500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>630800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>415500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>199100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>119500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>74600</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N46" s="3"/>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O46" s="3"/>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>238800</v>
+        <v>225900</v>
       </c>
       <c r="E47" s="3">
+        <v>238500</v>
+      </c>
+      <c r="F47" s="3">
         <v>244500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>244400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>68000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>58300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>30400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>13100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>10900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>300</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N47" s="3"/>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O47" s="3"/>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>15800</v>
+        <v>10400</v>
       </c>
       <c r="E48" s="3">
+        <v>15700</v>
+      </c>
+      <c r="F48" s="3">
         <v>24100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>38100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>42200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>24900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>400</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N48" s="3"/>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O48" s="3"/>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>19500</v>
+        <v>16700</v>
       </c>
       <c r="E49" s="3">
+        <v>19400</v>
+      </c>
+      <c r="F49" s="3">
         <v>27500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>31000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>31800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>13200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>10100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>200</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
-      </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N49" s="3"/>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O49" s="3"/>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2089,9 +2202,12 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-      <c r="N50" s="3"/>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3"/>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2125,45 +2241,51 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-      <c r="N51" s="3"/>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3"/>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E52" s="3">
         <v>9700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>7300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>600</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N52" s="3"/>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O52" s="3"/>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2197,45 +2319,51 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-      <c r="N53" s="3"/>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3"/>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>636300</v>
+        <v>528600</v>
       </c>
       <c r="E54" s="3">
+        <v>635500</v>
+      </c>
+      <c r="F54" s="3">
         <v>763700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>958000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>904300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>743200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>473800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>225200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>135300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>76000</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N54" s="3"/>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O54" s="3"/>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2250,8 +2378,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2266,173 +2395,186 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>106300</v>
+        <v>114600</v>
       </c>
       <c r="E57" s="3">
+        <v>106200</v>
+      </c>
+      <c r="F57" s="3">
         <v>138000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>231300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>298900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>287500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>157500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>109600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>76100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>37300</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N57" s="3"/>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O57" s="3"/>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>43200</v>
+      </c>
+      <c r="E58" s="3">
         <v>5600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>80400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>64200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>84700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1800</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N58" s="3"/>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O58" s="3"/>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>35400</v>
+        <v>29700</v>
       </c>
       <c r="E59" s="3">
+        <v>35300</v>
+      </c>
+      <c r="F59" s="3">
         <v>14800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>29100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>32800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>42300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>25500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>11600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>10300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2600</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N59" s="3"/>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O59" s="3"/>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>155300</v>
+        <v>195400</v>
       </c>
       <c r="E60" s="3">
+        <v>155100</v>
+      </c>
+      <c r="F60" s="3">
         <v>241900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>338800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>427300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>356400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>201800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>134800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>88200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>39900</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N60" s="3"/>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O60" s="3"/>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>123400</v>
+        <v>77200</v>
       </c>
       <c r="E61" s="3">
+        <v>123200</v>
+      </c>
+      <c r="F61" s="3">
         <v>103800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>125600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>27000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>11000</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -2445,9 +2587,12 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-      <c r="N61" s="3"/>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3"/>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2469,21 +2614,24 @@
       <c r="I62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J62" s="3">
+      <c r="J62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K62" s="3">
         <v>1200</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
+      <c r="L62" s="3">
+        <v>0</v>
       </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N62" s="3"/>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O62" s="3"/>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2517,9 +2665,12 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-      <c r="N63" s="3"/>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3"/>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2553,9 +2704,12 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-      <c r="N64" s="3"/>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3"/>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2589,45 +2743,51 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-      <c r="N65" s="3"/>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3"/>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>283100</v>
+        <v>275900</v>
       </c>
       <c r="E66" s="3">
+        <v>282800</v>
+      </c>
+      <c r="F66" s="3">
         <v>374500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>496200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>486100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>384500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>210700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>136400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>88200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>39900</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N66" s="3"/>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O66" s="3"/>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2642,8 +2802,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2677,9 +2838,12 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-      <c r="N68" s="3"/>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3"/>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2713,9 +2877,12 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-      <c r="N69" s="3"/>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3"/>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2738,20 +2905,23 @@
         <v>0</v>
       </c>
       <c r="J70" s="3">
+        <v>0</v>
+      </c>
+      <c r="K70" s="3">
         <v>53700</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>42900</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>39100</v>
       </c>
-      <c r="M70" s="3">
-        <v>0</v>
-      </c>
-      <c r="N70" s="3"/>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3"/>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2785,45 +2955,51 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-      <c r="N71" s="3"/>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3"/>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>103100</v>
+        <v>28600</v>
       </c>
       <c r="E72" s="3">
+        <v>104400</v>
+      </c>
+      <c r="F72" s="3">
         <v>136700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>200100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>173600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>130800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>49400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>20200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-5100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-8700</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N72" s="3"/>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O72" s="3"/>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2857,9 +3033,12 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-      <c r="N73" s="3"/>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3"/>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2893,9 +3072,12 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-      <c r="N74" s="3"/>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3"/>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2929,45 +3111,51 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-      <c r="N75" s="3"/>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3"/>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>351500</v>
+        <v>251600</v>
       </c>
       <c r="E76" s="3">
+        <v>350900</v>
+      </c>
+      <c r="F76" s="3">
         <v>387500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>459700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>418200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>359200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>263300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>34700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-3000</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N76" s="3"/>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O76" s="3"/>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3001,86 +3189,95 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-      <c r="N77" s="3"/>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3"/>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N80" s="2"/>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O80" s="2"/>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-29900</v>
+        <v>-75700</v>
       </c>
       <c r="E81" s="3">
-        <v>-41800</v>
+        <v>-31000</v>
       </c>
       <c r="F81" s="3">
+        <v>-43200</v>
+      </c>
+      <c r="G81" s="3">
         <v>21700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>35000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>82600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>49400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>25800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-8800</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N81" s="3"/>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O81" s="3"/>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3095,44 +3292,48 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E83" s="3">
         <v>5200</v>
       </c>
-      <c r="E83" s="3">
-        <v>6000</v>
-      </c>
       <c r="F83" s="3">
+        <v>6200</v>
+      </c>
+      <c r="G83" s="3">
         <v>5500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>300</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N83" s="3"/>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3"/>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3166,9 +3367,12 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-      <c r="N84" s="3"/>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3"/>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3202,9 +3406,12 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-      <c r="N85" s="3"/>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3"/>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3238,9 +3445,12 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-      <c r="N86" s="3"/>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3"/>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3274,9 +3484,12 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-      <c r="N87" s="3"/>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3"/>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3310,45 +3523,51 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-      <c r="N88" s="3"/>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3"/>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>42100</v>
+        <v>-24400</v>
       </c>
       <c r="E89" s="3">
-        <v>-114200</v>
+        <v>42600</v>
       </c>
       <c r="F89" s="3">
+        <v>-117100</v>
+      </c>
+      <c r="G89" s="3">
         <v>-36600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>24100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>61500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>102900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>36600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1000</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N89" s="3"/>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3"/>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3363,44 +3582,48 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-7200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-12800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-400</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N91" s="3"/>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O91" s="3"/>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3434,9 +3657,12 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-      <c r="N92" s="3"/>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3"/>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3470,45 +3696,51 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-      <c r="N93" s="3"/>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3"/>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E94" s="3">
         <v>7700</v>
       </c>
-      <c r="E94" s="3">
-        <v>-6100</v>
-      </c>
       <c r="F94" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="G94" s="3">
         <v>-168300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-31700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-16200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-47200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-6000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-13800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-700</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N94" s="3"/>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3"/>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3523,8 +3755,9 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3532,10 +3765,10 @@
         <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>5800</v>
+        <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>6300</v>
       </c>
       <c r="G96" s="3">
         <v>0</v>
@@ -3558,9 +3791,12 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-      <c r="N96" s="3"/>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3"/>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3594,9 +3830,12 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-      <c r="N97" s="3"/>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3"/>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3630,9 +3869,12 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-      <c r="N98" s="3"/>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3"/>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3666,115 +3908,127 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-      <c r="N99" s="3"/>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3"/>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-41600</v>
+        <v>500</v>
       </c>
       <c r="E100" s="3">
-        <v>41900</v>
+        <v>-41700</v>
       </c>
       <c r="F100" s="3">
+        <v>42400</v>
+      </c>
+      <c r="G100" s="3">
         <v>86700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>86500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>3700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>92900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>3100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>30700</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N100" s="3"/>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3"/>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-4800</v>
+        <v>-4200</v>
       </c>
       <c r="E101" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="F101" s="3">
+        <v>-14800</v>
+      </c>
+      <c r="G101" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="I101" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J101" s="3">
+        <v>8800</v>
+      </c>
+      <c r="K101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="L101" s="3">
         <v>700</v>
       </c>
-      <c r="F101" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-6600</v>
-      </c>
-      <c r="H101" s="3">
-        <v>1600</v>
-      </c>
-      <c r="I101" s="3">
-        <v>8800</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-500</v>
-      </c>
-      <c r="K101" s="3">
-        <v>700</v>
-      </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1500</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N101" s="3"/>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O101" s="3"/>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>3400</v>
+        <v>-29700</v>
       </c>
       <c r="E102" s="3">
-        <v>-77700</v>
+        <v>-700</v>
       </c>
       <c r="F102" s="3">
+        <v>-95800</v>
+      </c>
+      <c r="G102" s="3">
         <v>-120600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>72300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>50600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>157400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>33300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-9300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>30500</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N102" s="3"/>
+      <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/ZEPP_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ZEPP_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
   <si>
     <t>ZEPP</t>
   </si>
@@ -656,184 +656,196 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>258900</v>
+      </c>
+      <c r="E8" s="3">
         <v>182600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>352900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>613600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>983900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>985400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>834700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>530000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>314900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>216400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>128700</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O8" s="3"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="3"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>159700</v>
+      </c>
+      <c r="E9" s="3">
         <v>112400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>260500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>494800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>778300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>781300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>624000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>393400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>238900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>178000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>112900</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O9" s="3"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="3"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>99200</v>
+      </c>
+      <c r="E10" s="3">
         <v>70200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>92400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>118900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>205500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>204100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>210800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>136600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>76000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>38400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>15900</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O10" s="3"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10" s="3"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -849,47 +861,51 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>45300</v>
+      </c>
+      <c r="E12" s="3">
         <v>46200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>51500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>77300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>81100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>82400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>61900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>38300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>23600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>18400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>8800</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O12" s="3"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="3"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -926,87 +942,96 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-      <c r="O13" s="3"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E14" s="3">
         <v>8100</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>-6100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-2100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-10500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-400</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E15" s="3">
         <v>5000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>7700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>8700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>8200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>4200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>600</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
-      <c r="O15" s="3"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1019,86 +1044,93 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>288100</v>
+      </c>
+      <c r="E17" s="3">
         <v>229900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>383300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>675500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>969100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>958700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>747600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>476800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>286900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>214500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>134500</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O17" s="3"/>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P17" s="3"/>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-29200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-47300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-30500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-61900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>14800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>26700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>87100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>53200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>28000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-5800</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O18" s="3"/>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="3"/>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1114,107 +1146,114 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E20" s="3">
         <v>4900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-9100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-10800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O20" s="3"/>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3"/>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-26700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-47100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-22200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-44000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>33700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>30000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>91300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>55600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>29700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-5500</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O21" s="3"/>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3"/>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E22" s="3">
         <v>5600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>6800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>8400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>7100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>3500</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1227,90 +1266,99 @@
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
-      <c r="O22" s="3"/>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3"/>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-37500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-62100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-33500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-53200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>23200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>40000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>93500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>56500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>29900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>4000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-5600</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O23" s="3"/>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P23" s="3"/>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E24" s="3">
         <v>13700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-2400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-9900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>11200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>7600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>4200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-100</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O24" s="3"/>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3"/>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1347,87 +1395,96 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-      <c r="O25" s="3"/>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3"/>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-40100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-75800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-31100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-43300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>21600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>35200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>82300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>48900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>25700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-5400</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O26" s="3"/>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P26" s="3"/>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-40100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-75700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-31000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-43200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>21700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>35000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>82300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>16500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>7100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-8800</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O27" s="3"/>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P27" s="3"/>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1464,9 +1521,12 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-      <c r="O28" s="3"/>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3"/>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1494,8 +1554,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>3</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>3</v>
@@ -1503,9 +1563,12 @@
       <c r="N29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O29" s="3"/>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P29" s="3"/>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1542,9 +1605,12 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-      <c r="O30" s="3"/>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3"/>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1581,87 +1647,96 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-      <c r="O31" s="3"/>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3"/>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>9100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>10800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O32" s="3"/>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3"/>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-40100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-75700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-31000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-43200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>21700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>35000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>82600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>49400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>25800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-8800</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O33" s="3"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P33" s="3"/>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1698,92 +1773,101 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-      <c r="O34" s="3"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3"/>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-40100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-75700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-31000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-43200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>21700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>35000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>82600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>49400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>25800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-8800</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O35" s="3"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P35" s="3"/>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O38" s="2"/>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P38" s="2"/>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1799,8 +1883,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1816,359 +1901,387 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>57000</v>
+      </c>
+      <c r="E41" s="3">
         <v>91100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>133700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>128500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>231200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>348200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>259000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>209600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>56300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>21300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>31600</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O41" s="3"/>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P41" s="3"/>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>1000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>5200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>5000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>3600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>21400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1300</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O42" s="3"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P42" s="3"/>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>97600</v>
+      </c>
+      <c r="E43" s="3">
         <v>79100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>82000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>126200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>171300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>196100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>232700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>107300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>96500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>69300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>29500</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O43" s="3"/>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P43" s="3"/>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>72800</v>
+      </c>
+      <c r="E44" s="3">
         <v>56800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>84900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>148200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>196700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>186500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>128400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>70500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>38400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>26700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>12900</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O44" s="3"/>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P44" s="3"/>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>200</v>
+        <v>1600</v>
       </c>
       <c r="E45" s="3">
         <v>200</v>
       </c>
       <c r="F45" s="3">
+        <v>200</v>
+      </c>
+      <c r="G45" s="3">
         <v>700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>6800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>4700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>600</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O45" s="3"/>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3"/>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>293500</v>
+      </c>
+      <c r="E46" s="3">
         <v>251600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>316700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>428900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>618800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>739500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>630800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>415500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>199100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>119500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>74600</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O46" s="3"/>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P46" s="3"/>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>220000</v>
+      </c>
+      <c r="E47" s="3">
         <v>225900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>238500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>244500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>244400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>68000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>58300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>30400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>13100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>10900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>300</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O47" s="3"/>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3"/>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E48" s="3">
         <v>10400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>15700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>24100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>38100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>42200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>24900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>400</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O48" s="3"/>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P48" s="3"/>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>23200</v>
+      </c>
+      <c r="E49" s="3">
         <v>16700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>19400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>27500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>31000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>31800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>13200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>10100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>200</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
-      </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O49" s="3"/>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="N49" s="3">
+        <v>0</v>
+      </c>
+      <c r="O49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P49" s="3"/>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2205,9 +2318,12 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-      <c r="O50" s="3"/>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3"/>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2244,48 +2360,54 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-      <c r="O51" s="3"/>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3"/>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E52" s="3">
         <v>4600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>9700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>600</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O52" s="3"/>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P52" s="3"/>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2322,48 +2444,54 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-      <c r="O53" s="3"/>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3"/>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>564800</v>
+      </c>
+      <c r="E54" s="3">
         <v>528600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>635500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>763700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>958000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>904300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>743200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>473800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>225200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>135300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>76000</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O54" s="3"/>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P54" s="3"/>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2379,8 +2507,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2396,188 +2525,201 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>192800</v>
+      </c>
+      <c r="E57" s="3">
         <v>114600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>106200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>138000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>231300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>298900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>287500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>157500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>109600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>76100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>37300</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O57" s="3"/>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P57" s="3"/>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>56700</v>
+      </c>
+      <c r="E58" s="3">
         <v>43200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>80400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>64200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>84700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1800</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O58" s="3"/>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P58" s="3"/>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>29500</v>
+      </c>
+      <c r="E59" s="3">
         <v>29700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>35300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>14800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>29100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>32800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>42300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>25500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>11600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>10300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2600</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O59" s="3"/>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3"/>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>286800</v>
+      </c>
+      <c r="E60" s="3">
         <v>195400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>155100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>241900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>338800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>427300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>356400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>201800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>134800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>88200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>39900</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O60" s="3"/>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P60" s="3"/>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>60600</v>
+      </c>
+      <c r="E61" s="3">
         <v>77200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>123200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>103800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>125600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>27000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>11000</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -2590,9 +2732,12 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-      <c r="O61" s="3"/>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3"/>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2617,21 +2762,24 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3">
         <v>1200</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
+      <c r="M62" s="3">
+        <v>0</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="3"/>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3"/>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2668,9 +2816,12 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-      <c r="O63" s="3"/>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3"/>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2707,9 +2858,12 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-      <c r="O64" s="3"/>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3"/>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2746,48 +2900,54 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-      <c r="O65" s="3"/>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3"/>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>350300</v>
+      </c>
+      <c r="E66" s="3">
         <v>275900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>282800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>374500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>496200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>486100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>384500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>210700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>136400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>88200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>39900</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O66" s="3"/>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P66" s="3"/>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2803,8 +2963,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2841,9 +3002,12 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-      <c r="O68" s="3"/>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3"/>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2880,9 +3044,12 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-      <c r="O69" s="3"/>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3"/>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2908,20 +3075,23 @@
         <v>0</v>
       </c>
       <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3">
         <v>53700</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>42900</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>39100</v>
       </c>
-      <c r="N70" s="3">
-        <v>0</v>
-      </c>
-      <c r="O70" s="3"/>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3"/>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2958,48 +3128,54 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-      <c r="O71" s="3"/>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3"/>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="E72" s="3">
         <v>28600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>104400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>136700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>200100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>173600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>130800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>49400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>20200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-5100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-8700</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O72" s="3"/>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P72" s="3"/>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3036,9 +3212,12 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-      <c r="O73" s="3"/>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3"/>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3075,9 +3254,12 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-      <c r="O74" s="3"/>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3"/>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3114,48 +3296,54 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-      <c r="O75" s="3"/>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3"/>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>214500</v>
+      </c>
+      <c r="E76" s="3">
         <v>251600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>350900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>387500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>459700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>418200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>359200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>263300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>34700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-3000</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O76" s="3"/>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P76" s="3"/>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3192,92 +3380,101 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-      <c r="O77" s="3"/>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3"/>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O80" s="2"/>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P80" s="2"/>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-40100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-75700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-31000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-43200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>21700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>35000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>82600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>49400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>25800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-8800</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O81" s="3"/>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P81" s="3"/>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3293,47 +3490,51 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E83" s="3">
         <v>2600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>5200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>6200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>5500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>300</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O83" s="3"/>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3"/>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3370,9 +3571,12 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-      <c r="O84" s="3"/>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3"/>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3409,9 +3613,12 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-      <c r="O85" s="3"/>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3"/>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3448,9 +3655,12 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-      <c r="O86" s="3"/>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3"/>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3487,9 +3697,12 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-      <c r="O87" s="3"/>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3"/>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3526,48 +3739,54 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-      <c r="O88" s="3"/>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3"/>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-25700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-24400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>42600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-117100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-36600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>24100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>61500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>102900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>36600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1000</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O89" s="3"/>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P89" s="3"/>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3583,47 +3802,51 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-7200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-12800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-400</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O91" s="3"/>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P91" s="3"/>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3660,9 +3883,12 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-      <c r="O92" s="3"/>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3"/>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3699,48 +3925,54 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-      <c r="O93" s="3"/>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3"/>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>7700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-6200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-168300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-31700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-16200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-47200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-6000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-13800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-700</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O94" s="3"/>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3"/>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3756,8 +3988,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3768,11 +4001,11 @@
         <v>0</v>
       </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
         <v>6300</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
       <c r="H96" s="3">
         <v>0</v>
       </c>
@@ -3794,9 +4027,12 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-      <c r="O96" s="3"/>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3"/>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3833,9 +4069,12 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-      <c r="O97" s="3"/>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3"/>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3872,9 +4111,12 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-      <c r="O98" s="3"/>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3"/>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3911,124 +4153,136 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-      <c r="O99" s="3"/>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3"/>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>24800</v>
+      </c>
+      <c r="E100" s="3">
         <v>500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-41700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>42400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>86700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>86500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>3700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>92900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>3100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>30700</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O100" s="3"/>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3"/>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E101" s="3">
         <v>-4200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-9300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-14800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-2500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-6600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>8800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1500</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O101" s="3"/>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3"/>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-29700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-95800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-120600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>72300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>50600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>157400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>33300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-9300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>30500</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O102" s="3"/>
+      <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
